--- a/docs/informe tecnico (1).xlsx
+++ b/docs/informe tecnico (1).xlsx
@@ -1,14 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\INSTRUCTOR CarlosJulio\PROYECTO\entrega\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81AA4D06-ACBE-4535-82D3-46AD3D5E3347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Hoja1" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Hoja2" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Hoja3" sheetId="3" r:id="rId6"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="mYtFuBBLwN7b1GMZTty1RAlbOIVUK1YfomSSqH42+A8="/>
@@ -18,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="325">
   <si>
     <t>Requisitos para el cliente</t>
   </si>
@@ -999,362 +1008,114 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
       </rPr>
       <t>Cambios Realizados:</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
       </rPr>
       <t xml:space="preserve"> se modifico los roles que se solicito por que estaban mal definidos</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Aptos Narrow"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve">                                                           </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Aptos Narrow"/>
-        <b/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve">   actividades</t>
-    </r>
-  </si>
-  <si>
-    <t>MES 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                  MES 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                  MES 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                  MES 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                  MES 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                  MES 6</t>
-  </si>
-  <si>
-    <t>semana 1</t>
-  </si>
-  <si>
-    <t>semana 2</t>
-  </si>
-  <si>
-    <t>semana 3</t>
-  </si>
-  <si>
-    <t>semana 4</t>
-  </si>
-  <si>
-    <t>nombre</t>
-  </si>
-  <si>
-    <t>Actividades principales</t>
-  </si>
-  <si>
-    <t>1. Análisis de requerimientos</t>
-  </si>
-  <si>
-    <t>- Definir necesidades de usuarios y desarrolladores</t>
-  </si>
-  <si>
-    <t>- Especificar hardware y software</t>
-  </si>
-  <si>
-    <t>- Redactar documentación inicial</t>
-  </si>
-  <si>
-    <t>2. Diseño de la solución</t>
-  </si>
-  <si>
-    <t>- Diseño de la arquitectura de la app</t>
-  </si>
-  <si>
-    <t>- Bocetos de interfaz UX/UI</t>
-  </si>
-  <si>
-    <t>- Definir base de datos</t>
-  </si>
-  <si>
-    <t>3. Desarrollo inicial</t>
-  </si>
-  <si>
-    <t>- Configuración del entorno (Visual Studio, SDK Android)</t>
-  </si>
-  <si>
-    <t>- Desarrollo de módulos principales en C# (.NET MAUI)</t>
-  </si>
-  <si>
-    <t>- Conexión con servidor en la nube</t>
-  </si>
-  <si>
-    <t>4. Integración y mejoras</t>
-  </si>
-  <si>
-    <t>- Añadir funciones extra</t>
-  </si>
-  <si>
-    <t>- Optimización del rendimiento</t>
-  </si>
-  <si>
-    <t>- Ajustes de accesibilidad</t>
-  </si>
-  <si>
-    <t>5. Pruebas y validación</t>
-  </si>
-  <si>
-    <t>- Pruebas funcionales</t>
-  </si>
-  <si>
-    <t>- Pruebas con usuarios sordomudos y oyentes</t>
-  </si>
-  <si>
-    <t>- Corrección de errores</t>
-  </si>
-  <si>
-    <t>6. Implementación y lanzamiento</t>
-  </si>
-  <si>
-    <t>- Publicación en Play Store</t>
-  </si>
-  <si>
-    <t>- Manual de usuario</t>
-  </si>
-  <si>
-    <t>- Capacitación y difusión</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
-      </rPr>
-      <t>Informe de Cambios y Coherencia del Proyecto</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve">
-Este informe presenta la actualización y corrección de las incoherencias identificadas en la planificación inicial del proyecto "Traduce Señas – Signia". Se han revisado y ajustado el presupuesto, los roles del equipo y el plan de trabajo para garantizar una ejecución más precisa y viable.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
-      </rPr>
-      <t>1. Presupuesto y Coherencia Económica</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve">
-Incoherencia Detectada:
-Se identificó que el presupuesto estimado no concordaba con la realidad y que la licencia del proyecto no especificaba una tarifa de uso fija para fines comerciales.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve">
-Cambios Realizados y Justificación:</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve">
-Ajuste del Presupuesto Estimado: La Propuesta Técnica y Económica.docx presenta un presupuesto total de $51,350,000 COP, que incluye costos de desarrollo, infraestructura, pruebas y capacitación. Aunque los precios específicos de los componentes individuales no se detallan en los documentos proporcionados, el informe técnico (hojas 1 y 2) sugiere que el presupuesto se ha ajustado para reflejar los costos de hardware y software (como el costo de un portátil, licencias de software, etc.).
-Definición de Tarifa de Licencia: La Licencia del Proyecto.docx fue modificada para incluir una tarifa de licencia para usos comerciales. Se estableció una cuota base de $2,000,000 COP mensuales, lo que proporciona un flujo de ingresos definido y cubre los costos de soporte, actualizaciones y mantenimiento. Este cambio dota de mayor solidez financiera al proyecto a mediano y largo plazo.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
-      </rPr>
-      <t>2. Equipo de Trabajo y Roles</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve">
-Incoherencia Detectada:
-Los roles y responsabilidades del equipo de trabajo estaban mal definidos o no coincidían entre los documentos.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
-      </rPr>
-      <t>Cambios Realizados y Justificación:</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve">
-Reasignación y Clarificación de Roles: Se corrigió la designación de los roles para que fueran coherentes en la Especificación de Requisitos de Software.docx y el informe tecnico.xlsx - Hoja3.csv. Se asignaron roles específicos a cada miembro del equipo:
-Juan Mauricio Suaza: Líder del Proyecto y Analista/Desarrollador, con responsabilidades de coordinación y seguimiento.
-Juan Camilo Fierro y Luis Alejandro Duarte: Analistas/Desarrolladores, enfocados en la programación de la aplicación, integración con el servidor y la base de datos, además de asegurar la accesibilidad para personas con discapacidad.
-Justificación: La redefinición de roles asegura que las responsabilidades se alineen con las capacidades de cada integrante, optimizando la productividad y la calidad del trabajo. Esto elimina la confusión y garantiza que cada fase del proyecto sea manejada por el especialista adecuado.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
-      </rPr>
-      <t>3. Plan de Trabajo y Cronograma</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve">
-Incoherencia Detectada:
-El plan de trabajo inicial asignaba una duración de un mes a cada fase, lo cual era incorrecto e inflexible, ya que algunas fases eran más cortas y otras más largas.
-Cambios Realizados y Justificación:
-Ajuste de Duración de las Fases: El plan de trabajo detallado en la Propuesta Técnica y Económica.docx y en el informe tecnico.xlsx - Hoja3.csv fue modificado para reflejar un cronograma más realista:
-Fase 1 (Análisis de requerimientos): 3 semanas.
-Fase 2 (Diseño de la solución): 5 semanas.
-Fase 3 (Desarrollo inicial): 5 semanas.
-Fase 4 (Integración y mejora): 4 semanas.
-Fase 5 (Pruebas y validación): 5 semanas.
-Justificación: El nuevo cronograma es más preciso y se alinea con el esfuerzo real requerido para cada actividad. Este cambio permite una mejor gestión del tiempo, evita retrasos innecesarios y asegura que el proyecto avance de manera eficiente y controlada. La flexibilidad de este plan es fundamental para la correcta finalización del proyecto.</t>
     </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="17">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="15">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
-    <font/>
     <font>
-      <sz val="10.0"/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="6.0"/>
+      <sz val="6"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="9"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF8ED873"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="24.0"/>
+      <sz val="24"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color rgb="FFFFC000"/>
-      <name val="Aptos Narrow"/>
-    </font>
   </fonts>
-  <fills count="19">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1400,93 +1161,52 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA6C9EB"/>
-        <bgColor rgb="FFA6C9EB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE2D5"/>
-        <bgColor rgb="FFFAE2D5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor rgb="FF00B0F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAEAEAE"/>
-        <bgColor rgb="FFAEAEAE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED873"/>
-        <bgColor rgb="FF8ED873"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor theme="0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFBFBF"/>
-        <bgColor rgb="FFBFBFBF"/>
+        <bgColor theme="9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="73">
-    <border/>
+  <borders count="26">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
@@ -1496,6 +1216,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -1507,35 +1228,50 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -1544,38 +1280,53 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -1590,27 +1341,34 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -1620,8 +1378,10 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
@@ -1631,6 +1391,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -1645,27 +1406,34 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -1675,8 +1443,10 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
@@ -1686,6 +1456,7 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1700,841 +1471,165 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="63">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="9" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="16" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="17" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="18" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="19" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="20" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="21" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="22" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="23" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="24" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="25" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="6" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="25" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="25" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="7" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="11" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="25" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="25" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="25" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="25" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="25" fillId="4" fontId="13" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="25" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="26" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="27" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="28" fillId="10" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="29" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="30" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="31" fillId="11" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="28" fillId="12" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="28" fillId="13" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="28" fillId="14" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="28" fillId="15" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="32" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="33" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="34" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="35" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="36" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="37" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="35" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="36" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="38" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="39" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="40" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="38" fillId="13" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="39" fillId="13" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="40" fillId="13" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="38" fillId="14" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="39" fillId="14" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="40" fillId="14" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="38" fillId="15" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="39" fillId="15" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="40" fillId="15" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="41" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="42" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="43" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="44" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="45" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="46" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="47" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="48" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="49" fillId="10" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="25" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="50" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="49" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="51" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="25" fillId="10" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="52" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="53" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="38" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="16" fontId="15" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="39" fillId="10" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="40" fillId="17" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="39" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="40" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="54" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="55" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="56" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="57" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="58" fillId="11" fontId="16" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="56" fillId="11" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="58" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="25" fillId="11" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="59" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="60" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="61" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="62" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="63" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="62" fillId="11" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="63" fillId="11" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="51" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="64" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="46" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="44" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="45" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="45" fillId="11" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="46" fillId="12" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="25" fillId="12" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="62" fillId="12" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="63" fillId="12" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="46" fillId="13" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="25" fillId="13" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="65" fillId="0" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="62" fillId="13" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="63" fillId="13" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="45" fillId="13" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="46" fillId="14" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="49" fillId="14" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="25" fillId="14" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="62" fillId="14" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="63" fillId="14" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="46" fillId="18" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="25" fillId="18" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="66" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="67" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="68" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="69" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="70" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="69" fillId="18" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="70" fillId="18" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="71" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="72" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -2724,32 +1819,35 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.63"/>
-    <col customWidth="1" min="2" max="2" width="55.63"/>
-    <col customWidth="1" min="3" max="8" width="10.63"/>
-    <col customWidth="1" min="9" max="9" width="11.63"/>
-    <col customWidth="1" min="10" max="10" width="28.75"/>
-    <col customWidth="1" min="11" max="12" width="23.25"/>
-    <col customWidth="1" min="13" max="14" width="23.0"/>
-    <col customWidth="1" min="15" max="15" width="22.88"/>
-    <col customWidth="1" min="16" max="16" width="32.88"/>
-    <col customWidth="1" min="17" max="17" width="21.88"/>
-    <col customWidth="1" min="18" max="19" width="10.63"/>
-    <col customWidth="1" min="20" max="20" width="33.88"/>
-    <col customWidth="1" min="21" max="26" width="10.63"/>
+    <col min="1" max="1" width="10.59765625" customWidth="1"/>
+    <col min="2" max="2" width="55.59765625" customWidth="1"/>
+    <col min="3" max="3" width="27.69921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="10.59765625" customWidth="1"/>
+    <col min="9" max="9" width="11.59765625" customWidth="1"/>
+    <col min="10" max="10" width="28.69921875" customWidth="1"/>
+    <col min="11" max="12" width="23.19921875" customWidth="1"/>
+    <col min="13" max="14" width="23" customWidth="1"/>
+    <col min="15" max="15" width="22.8984375" customWidth="1"/>
+    <col min="16" max="16" width="32.8984375" customWidth="1"/>
+    <col min="17" max="17" width="21.8984375" customWidth="1"/>
+    <col min="18" max="19" width="10.59765625" customWidth="1"/>
+    <col min="20" max="20" width="33.8984375" customWidth="1"/>
+    <col min="21" max="26" width="10.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:21" ht="13.8">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2772,173 +1870,173 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:21" ht="14.4">
       <c r="A4" s="2"/>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5">
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="42"/>
+    </row>
+    <row r="5" spans="1:21" ht="13.8">
       <c r="A5" s="2"/>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="7" t="s">
+      <c r="D5" s="46"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="10"/>
-    </row>
-    <row r="6">
+      <c r="G5" s="46"/>
+      <c r="H5" s="51"/>
+    </row>
+    <row r="6" spans="1:21" ht="13.8">
       <c r="A6" s="2"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="15"/>
-    </row>
-    <row r="7">
+      <c r="B6" s="44"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="52"/>
+    </row>
+    <row r="7" spans="1:21" ht="14.4">
       <c r="A7" s="2"/>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="17" t="s">
+      <c r="D7" s="54"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="18"/>
-      <c r="H7" s="20"/>
-    </row>
-    <row r="8">
+      <c r="G7" s="54"/>
+      <c r="H7" s="56"/>
+    </row>
+    <row r="8" spans="1:21" ht="14.4">
       <c r="A8" s="2"/>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="17" t="s">
+      <c r="D8" s="54"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="18"/>
-      <c r="H8" s="20"/>
-    </row>
-    <row r="9">
+      <c r="G8" s="54"/>
+      <c r="H8" s="56"/>
+    </row>
+    <row r="9" spans="1:21" ht="14.4">
       <c r="A9" s="2"/>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="17" t="s">
+      <c r="D9" s="54"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="18"/>
-      <c r="H9" s="20"/>
-    </row>
-    <row r="10">
+      <c r="G9" s="54"/>
+      <c r="H9" s="56"/>
+    </row>
+    <row r="10" spans="1:21" ht="14.4">
       <c r="A10" s="2"/>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="22" t="s">
+      <c r="D10" s="54"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="18"/>
-      <c r="H10" s="20"/>
-    </row>
-    <row r="11">
+      <c r="G10" s="54"/>
+      <c r="H10" s="56"/>
+    </row>
+    <row r="11" spans="1:21" ht="14.4">
       <c r="A11" s="2"/>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="17" t="s">
+      <c r="D11" s="54"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="18"/>
-      <c r="H11" s="20"/>
-    </row>
-    <row r="12">
+      <c r="G11" s="54"/>
+      <c r="H11" s="56"/>
+    </row>
+    <row r="12" spans="1:21" ht="14.4">
       <c r="A12" s="2"/>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="17" t="s">
+      <c r="D12" s="54"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="18"/>
-      <c r="H12" s="20"/>
-    </row>
-    <row r="13">
+      <c r="G12" s="54"/>
+      <c r="H12" s="56"/>
+    </row>
+    <row r="13" spans="1:21" ht="14.4">
       <c r="A13" s="2"/>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="17" t="s">
+      <c r="D13" s="54"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="18"/>
-      <c r="H13" s="20"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="23" t="s">
+      <c r="G13" s="54"/>
+      <c r="H13" s="56"/>
+    </row>
+    <row r="14" spans="1:21" ht="14.4">
+      <c r="B14" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="25"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="24" t="s">
+      <c r="D14" s="58"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="25"/>
-      <c r="H14" s="27"/>
-      <c r="L14" s="28"/>
-    </row>
-    <row r="17">
+      <c r="G14" s="58"/>
+      <c r="H14" s="60"/>
+      <c r="L14" s="6"/>
+    </row>
+    <row r="17" spans="1:21" ht="13.8">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -2961,556 +2059,556 @@
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="J21" s="29" t="s">
+    <row r="21" spans="1:21" ht="15.75" customHeight="1">
+      <c r="J21" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="K21" s="30" t="s">
+      <c r="K21" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="L21" s="30" t="s">
+      <c r="L21" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="M21" s="30" t="s">
+      <c r="M21" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="N21" s="30" t="s">
+      <c r="N21" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="O21" s="30" t="s">
+      <c r="O21" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="P21" s="30" t="s">
+      <c r="P21" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="K22" s="31" t="s">
+    <row r="22" spans="1:21" ht="15.75" customHeight="1">
+      <c r="K22" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="L22" s="31" t="s">
+      <c r="L22" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="M22" s="31" t="s">
+      <c r="M22" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="N22" s="31" t="s">
+      <c r="N22" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="O22" s="31" t="s">
+      <c r="O22" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="P22" s="31" t="s">
+      <c r="P22" s="9" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="K23" s="31" t="s">
+    <row r="23" spans="1:21" ht="15.75" customHeight="1">
+      <c r="K23" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="L23" s="31" t="s">
+      <c r="L23" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="M23" s="31" t="s">
+      <c r="M23" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="N23" s="31" t="s">
+      <c r="N23" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="O23" s="31" t="s">
+      <c r="O23" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="P23" s="31" t="s">
+      <c r="P23" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="K24" s="31" t="s">
+    <row r="24" spans="1:21" ht="15.75" customHeight="1">
+      <c r="K24" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L24" s="31" t="s">
+      <c r="L24" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="M24" s="31" t="s">
+      <c r="M24" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="N24" s="31" t="s">
+      <c r="N24" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="O24" s="31" t="s">
+      <c r="O24" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="P24" s="31" t="s">
+      <c r="P24" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="K25" s="31" t="s">
+    <row r="25" spans="1:21" ht="15.75" customHeight="1">
+      <c r="K25" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="L25" s="31" t="s">
+      <c r="L25" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="M25" s="31" t="s">
+      <c r="M25" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="N25" s="31" t="s">
+      <c r="N25" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="O25" s="31" t="s">
+      <c r="O25" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="P25" s="31" t="s">
+      <c r="P25" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="K26" s="31" t="s">
+    <row r="26" spans="1:21" ht="15.75" customHeight="1">
+      <c r="K26" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L26" s="31" t="s">
+      <c r="L26" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="M26" s="31" t="s">
+      <c r="M26" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="N26" s="31" t="s">
+      <c r="N26" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="O26" s="31" t="s">
+      <c r="O26" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="P26" s="31" t="s">
+      <c r="P26" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="K27" s="31" t="s">
+    <row r="27" spans="1:21" ht="15.75" customHeight="1">
+      <c r="K27" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="L27" s="31" t="s">
+      <c r="L27" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="M27" s="31" t="s">
+      <c r="M27" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="N27" s="31" t="s">
+      <c r="N27" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="O27" s="31" t="s">
+      <c r="O27" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="P27" s="31" t="s">
+      <c r="P27" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="K28" s="31" t="s">
+    <row r="28" spans="1:21" ht="15.75" customHeight="1">
+      <c r="K28" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="L28" s="31" t="s">
+      <c r="L28" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="M28" s="31" t="s">
+      <c r="M28" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="N28" s="31" t="s">
+      <c r="N28" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="O28" s="31" t="s">
+      <c r="O28" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="P28" s="31" t="s">
+      <c r="P28" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="K29" s="31" t="s">
+    <row r="29" spans="1:21" ht="15.75" customHeight="1">
+      <c r="K29" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="L29" s="31" t="s">
+      <c r="L29" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="M29" s="31" t="s">
+      <c r="M29" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="N29" s="31" t="s">
+      <c r="N29" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="O29" s="31" t="s">
+      <c r="O29" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="P29" s="31" t="s">
+      <c r="P29" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="J32" s="32"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="J35" s="29" t="s">
+    <row r="30" spans="1:21" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:21" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:21" ht="15.75" customHeight="1">
+      <c r="J32" s="10"/>
+    </row>
+    <row r="33" spans="10:16" ht="15.75" customHeight="1"/>
+    <row r="34" spans="10:16" ht="15.75" customHeight="1"/>
+    <row r="35" spans="10:16" ht="15.75" customHeight="1">
+      <c r="J35" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="K35" s="30" t="s">
+      <c r="K35" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="L35" s="30" t="s">
+      <c r="L35" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="M35" s="30" t="s">
+      <c r="M35" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="N35" s="30" t="s">
+      <c r="N35" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="O35" s="30" t="s">
+      <c r="O35" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="P35" s="30" t="s">
+      <c r="P35" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="K36" s="31" t="s">
+    <row r="36" spans="10:16" ht="15.75" customHeight="1">
+      <c r="K36" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="L36" s="31" t="s">
+      <c r="L36" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="M36" s="31" t="s">
+      <c r="M36" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="N36" s="31" t="s">
+      <c r="N36" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="O36" s="31" t="s">
+      <c r="O36" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="P36" s="31" t="s">
+      <c r="P36" s="9" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="K37" s="31" t="s">
+    <row r="37" spans="10:16" ht="15.75" customHeight="1">
+      <c r="K37" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="L37" s="31" t="s">
+      <c r="L37" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="M37" s="31" t="s">
+      <c r="M37" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="N37" s="31" t="s">
+      <c r="N37" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="O37" s="31" t="s">
+      <c r="O37" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="P37" s="31" t="s">
+      <c r="P37" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="K38" s="31" t="s">
+    <row r="38" spans="10:16" ht="15.75" customHeight="1">
+      <c r="K38" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L38" s="31" t="s">
+      <c r="L38" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="M38" s="31" t="s">
+      <c r="M38" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="N38" s="31" t="s">
+      <c r="N38" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="O38" s="31" t="s">
+      <c r="O38" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="P38" s="31" t="s">
+      <c r="P38" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="K39" s="31" t="s">
+    <row r="39" spans="10:16" ht="15.75" customHeight="1">
+      <c r="K39" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="L39" s="31" t="s">
+      <c r="L39" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="M39" s="31" t="s">
+      <c r="M39" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="N39" s="31" t="s">
+      <c r="N39" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="O39" s="31" t="s">
+      <c r="O39" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="P39" s="31" t="s">
+      <c r="P39" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="K40" s="31" t="s">
+    <row r="40" spans="10:16" ht="15.75" customHeight="1">
+      <c r="K40" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L40" s="31" t="s">
+      <c r="L40" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="M40" s="31" t="s">
+      <c r="M40" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="N40" s="31" t="s">
+      <c r="N40" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="O40" s="31" t="s">
+      <c r="O40" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="P40" s="31" t="s">
+      <c r="P40" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="K41" s="31" t="s">
+    <row r="41" spans="10:16" ht="15.75" customHeight="1">
+      <c r="K41" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="L41" s="31" t="s">
+      <c r="L41" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="M41" s="31" t="s">
+      <c r="M41" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="N41" s="31" t="s">
+      <c r="N41" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="O41" s="31" t="s">
+      <c r="O41" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="P41" s="31" t="s">
+      <c r="P41" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="K42" s="31" t="s">
+    <row r="42" spans="10:16" ht="15.75" customHeight="1">
+      <c r="K42" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="L42" s="31" t="s">
+      <c r="L42" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="M42" s="31" t="s">
+      <c r="M42" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="N42" s="31" t="s">
+      <c r="N42" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="O42" s="31" t="s">
+      <c r="O42" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="P42" s="31" t="s">
+      <c r="P42" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="J48" s="29" t="s">
+    <row r="43" spans="10:16" ht="15.75" customHeight="1"/>
+    <row r="44" spans="10:16" ht="15.75" customHeight="1"/>
+    <row r="45" spans="10:16" ht="15.75" customHeight="1"/>
+    <row r="46" spans="10:16" ht="15.75" customHeight="1"/>
+    <row r="47" spans="10:16" ht="15.75" customHeight="1"/>
+    <row r="48" spans="10:16" ht="15.75" customHeight="1">
+      <c r="J48" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="K48" s="30" t="s">
+      <c r="K48" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="L48" s="30" t="s">
+      <c r="L48" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="M48" s="30" t="s">
+      <c r="M48" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="N48" s="30" t="s">
+      <c r="N48" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="O48" s="30" t="s">
+      <c r="O48" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="P48" s="30" t="s">
+      <c r="P48" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="K49" s="31" t="s">
+    <row r="49" spans="11:16" ht="15.75" customHeight="1">
+      <c r="K49" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="L49" s="31" t="s">
+      <c r="L49" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="M49" s="31" t="s">
+      <c r="M49" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="N49" s="31" t="s">
+      <c r="N49" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="O49" s="31" t="s">
+      <c r="O49" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="P49" s="31" t="s">
+      <c r="P49" s="9" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="K50" s="31" t="s">
+    <row r="50" spans="11:16" ht="15.75" customHeight="1">
+      <c r="K50" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="L50" s="31" t="s">
+      <c r="L50" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="M50" s="31" t="s">
+      <c r="M50" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="N50" s="31" t="s">
+      <c r="N50" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="O50" s="31" t="s">
+      <c r="O50" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="P50" s="31" t="s">
+      <c r="P50" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="K51" s="31" t="s">
+    <row r="51" spans="11:16" ht="15.75" customHeight="1">
+      <c r="K51" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L51" s="31" t="s">
+      <c r="L51" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="M51" s="31" t="s">
+      <c r="M51" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="N51" s="31" t="s">
+      <c r="N51" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="O51" s="31" t="s">
+      <c r="O51" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="P51" s="31" t="s">
+      <c r="P51" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="K52" s="31" t="s">
+    <row r="52" spans="11:16" ht="15.75" customHeight="1">
+      <c r="K52" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="L52" s="31" t="s">
+      <c r="L52" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="M52" s="31" t="s">
+      <c r="M52" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="N52" s="31" t="s">
+      <c r="N52" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="O52" s="31" t="s">
+      <c r="O52" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="P52" s="31" t="s">
+      <c r="P52" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="K53" s="31" t="s">
+    <row r="53" spans="11:16" ht="15.75" customHeight="1">
+      <c r="K53" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L53" s="31" t="s">
+      <c r="L53" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="M53" s="31" t="s">
+      <c r="M53" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="N53" s="31" t="s">
+      <c r="N53" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="O53" s="31" t="s">
+      <c r="O53" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="P53" s="31" t="s">
+      <c r="P53" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="K54" s="31" t="s">
+    <row r="54" spans="11:16" ht="15.75" customHeight="1">
+      <c r="K54" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="L54" s="31" t="s">
+      <c r="L54" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="M54" s="31" t="s">
+      <c r="M54" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="N54" s="31" t="s">
+      <c r="N54" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="O54" s="31" t="s">
+      <c r="O54" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="P54" s="31" t="s">
+      <c r="P54" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="K55" s="31" t="s">
+    <row r="55" spans="11:16" ht="15.75" customHeight="1">
+      <c r="K55" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="L55" s="31" t="s">
+      <c r="L55" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="M55" s="31" t="s">
+      <c r="M55" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="N55" s="31" t="s">
+      <c r="N55" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="O55" s="31" t="s">
+      <c r="O55" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="P55" s="31" t="s">
+      <c r="P55" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="K56" s="31" t="s">
+    <row r="56" spans="11:16" ht="15.75" customHeight="1">
+      <c r="K56" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="L56" s="31" t="s">
+      <c r="L56" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="M56" s="31" t="s">
+      <c r="M56" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="N56" s="31" t="s">
+      <c r="N56" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="O56" s="31" t="s">
+      <c r="O56" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="P56" s="31" t="s">
+      <c r="P56" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="57" spans="11:16" ht="15.75" customHeight="1"/>
+    <row r="58" spans="11:16" ht="15.75" customHeight="1"/>
+    <row r="59" spans="11:16" ht="15.75" customHeight="1"/>
+    <row r="60" spans="11:16" ht="15.75" customHeight="1"/>
+    <row r="61" spans="11:16" ht="15.75" customHeight="1"/>
+    <row r="62" spans="11:16" ht="15.75" customHeight="1"/>
+    <row r="63" spans="11:16" ht="15.75" customHeight="1"/>
+    <row r="64" spans="11:16" ht="15.75" customHeight="1"/>
+    <row r="65" spans="1:21" ht="15.75" customHeight="1">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -3533,135 +2631,135 @@
       <c r="T65" s="1"/>
       <c r="U65" s="1"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="B68" s="33" t="s">
+    <row r="66" spans="1:21" ht="15.75" customHeight="1"/>
+    <row r="67" spans="1:21" ht="15.75" customHeight="1"/>
+    <row r="68" spans="1:21" ht="14.4">
+      <c r="B68" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C68" s="33"/>
-      <c r="D68" s="33"/>
-      <c r="E68" s="34"/>
-      <c r="F68" s="35"/>
-      <c r="G68" s="35"/>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="B69" s="36" t="s">
+      <c r="C68" s="11"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="62"/>
+      <c r="G68" s="62"/>
+    </row>
+    <row r="69" spans="1:21" ht="15.75" customHeight="1">
+      <c r="B69" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C69" s="36" t="s">
+      <c r="C69" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="D69" s="36" t="s">
+      <c r="D69" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E69" s="36" t="s">
+      <c r="E69" s="13" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="B70" s="37" t="s">
+    <row r="70" spans="1:21" ht="15.75" customHeight="1">
+      <c r="B70" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="C70" s="38" t="s">
+      <c r="C70" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="D70" s="38" t="s">
+      <c r="D70" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="E70" s="38" t="s">
+      <c r="E70" s="15" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="1:21" ht="15.75" customHeight="1">
       <c r="A71" s="2"/>
-      <c r="B71" s="37" t="s">
+      <c r="B71" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="C71" s="38" t="s">
+      <c r="C71" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="D71" s="38" t="s">
+      <c r="D71" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E71" s="38" t="s">
+      <c r="E71" s="15" t="s">
         <v>118</v>
       </c>
       <c r="R71" s="2"/>
       <c r="S71" s="2"/>
       <c r="T71" s="2"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="B72" s="37" t="s">
+    <row r="72" spans="1:21" ht="15.75" customHeight="1">
+      <c r="B72" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C72" s="38" t="s">
+      <c r="C72" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="D72" s="38" t="s">
+      <c r="D72" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E72" s="38" t="s">
+      <c r="E72" s="15" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="B73" s="37" t="s">
+    <row r="73" spans="1:21" ht="15.75" customHeight="1">
+      <c r="B73" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C73" s="38" t="s">
+      <c r="C73" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="D73" s="38" t="s">
+      <c r="D73" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="E73" s="38" t="s">
+      <c r="E73" s="15" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="B74" s="37" t="s">
+    <row r="74" spans="1:21" ht="15.75" customHeight="1">
+      <c r="B74" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="C74" s="38" t="s">
+      <c r="C74" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="D74" s="38" t="s">
+      <c r="D74" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="E74" s="38" t="s">
+      <c r="E74" s="15" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="B75" s="37" t="s">
+    <row r="75" spans="1:21" ht="15.75" customHeight="1">
+      <c r="B75" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="C75" s="38" t="s">
+      <c r="C75" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="D75" s="38" t="s">
+      <c r="D75" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="E75" s="38" t="s">
+      <c r="E75" s="15" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="B76" s="37" t="s">
+    <row r="76" spans="1:21" ht="15.75" customHeight="1">
+      <c r="B76" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="C76" s="38" t="s">
+      <c r="C76" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="D76" s="38" t="s">
+      <c r="D76" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="E76" s="38" t="s">
+      <c r="E76" s="15" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" spans="1:21" ht="15.75" customHeight="1">
       <c r="K77" s="2"/>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -3670,7 +2768,7 @@
       <c r="P77" s="2"/>
       <c r="Q77" s="2"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" spans="1:21" ht="15.75" customHeight="1">
       <c r="K78" s="2"/>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -3679,7 +2777,7 @@
       <c r="P78" s="2"/>
       <c r="Q78" s="2"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" spans="1:21" ht="15.75" customHeight="1">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3702,32 +2800,32 @@
       <c r="T79" s="1"/>
       <c r="U79" s="1"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="80" spans="1:21" ht="15.75" customHeight="1"/>
+    <row r="81" spans="1:20" ht="15.75" customHeight="1"/>
+    <row r="82" spans="1:20" ht="15.75" customHeight="1"/>
+    <row r="83" spans="1:20" ht="15.75" customHeight="1"/>
+    <row r="84" spans="1:20" ht="15.75" customHeight="1">
       <c r="A84" s="2"/>
       <c r="R84" s="2"/>
       <c r="S84" s="2"/>
       <c r="T84" s="2"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" spans="1:20" ht="15.75" customHeight="1">
       <c r="R85" s="2"/>
       <c r="S85" s="2"/>
       <c r="T85" s="2"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="86" spans="1:20" ht="15.75" customHeight="1"/>
+    <row r="87" spans="1:20" ht="15.75" customHeight="1"/>
+    <row r="88" spans="1:20" ht="15.75" customHeight="1"/>
+    <row r="89" spans="1:20" ht="15.75" customHeight="1"/>
+    <row r="90" spans="1:20" ht="15.75" customHeight="1"/>
+    <row r="91" spans="1:20" ht="15.75" customHeight="1"/>
+    <row r="92" spans="1:20" ht="15.75" customHeight="1"/>
+    <row r="93" spans="1:20" ht="15.75" customHeight="1"/>
+    <row r="94" spans="1:20" ht="15.75" customHeight="1"/>
+    <row r="95" spans="1:20" ht="15.75" customHeight="1"/>
+    <row r="96" spans="1:20" ht="15.75" customHeight="1"/>
     <row r="97" ht="15.75" customHeight="1"/>
     <row r="98" ht="15.75" customHeight="1"/>
     <row r="99" ht="15.75" customHeight="1"/>
@@ -4634,17 +3732,6 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:E6"/>
-    <mergeCell ref="F5:H6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="F13:H13"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="C8:E8"/>
@@ -4654,37 +3741,44 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:E6"/>
+    <mergeCell ref="F5:H6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F7:H7"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:U1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.63"/>
-    <col customWidth="1" min="2" max="2" width="24.75"/>
-    <col customWidth="1" min="3" max="3" width="37.75"/>
-    <col customWidth="1" min="4" max="9" width="10.63"/>
-    <col customWidth="1" min="10" max="10" width="23.0"/>
-    <col customWidth="1" min="11" max="11" width="57.0"/>
-    <col customWidth="1" min="12" max="12" width="32.88"/>
-    <col customWidth="1" min="13" max="13" width="44.75"/>
-    <col customWidth="1" min="14" max="14" width="38.63"/>
-    <col customWidth="1" min="15" max="15" width="25.88"/>
-    <col customWidth="1" min="16" max="18" width="10.63"/>
-    <col customWidth="1" min="19" max="19" width="85.13"/>
-    <col customWidth="1" min="20" max="26" width="10.63"/>
+    <col min="1" max="1" width="10.59765625" customWidth="1"/>
+    <col min="2" max="2" width="24.69921875" customWidth="1"/>
+    <col min="3" max="3" width="37.69921875" customWidth="1"/>
+    <col min="4" max="9" width="10.59765625" customWidth="1"/>
+    <col min="10" max="10" width="23" customWidth="1"/>
+    <col min="11" max="11" width="57" customWidth="1"/>
+    <col min="12" max="12" width="32.8984375" customWidth="1"/>
+    <col min="13" max="13" width="44.69921875" customWidth="1"/>
+    <col min="14" max="14" width="38.59765625" customWidth="1"/>
+    <col min="15" max="15" width="25.8984375" customWidth="1"/>
+    <col min="16" max="18" width="10.59765625" customWidth="1"/>
+    <col min="19" max="19" width="85.09765625" customWidth="1"/>
+    <col min="20" max="26" width="10.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:21" ht="13.8">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4707,147 +3801,147 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
     </row>
-    <row r="4">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:21" ht="14.4">
+      <c r="B4" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="6" t="s">
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="42"/>
+    </row>
+    <row r="5" spans="1:21" ht="13.8">
+      <c r="B5" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="7" t="s">
+      <c r="D5" s="46"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="10"/>
-    </row>
-    <row r="6">
-      <c r="B6" s="11"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="15"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="16" t="s">
+      <c r="G5" s="46"/>
+      <c r="H5" s="51"/>
+    </row>
+    <row r="6" spans="1:21" ht="13.8">
+      <c r="B6" s="44"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="52"/>
+    </row>
+    <row r="7" spans="1:21" ht="14.4">
+      <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="53" t="s">
         <v>137</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="17" t="s">
+      <c r="D7" s="54"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="53" t="s">
         <v>138</v>
       </c>
-      <c r="G7" s="18"/>
-      <c r="H7" s="20"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="16" t="s">
+      <c r="G7" s="54"/>
+      <c r="H7" s="56"/>
+    </row>
+    <row r="8" spans="1:21" ht="14.4">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="53" t="s">
         <v>139</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="17" t="s">
+      <c r="D8" s="54"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="G8" s="18"/>
-      <c r="H8" s="20"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="16" t="s">
+      <c r="G8" s="54"/>
+      <c r="H8" s="56"/>
+    </row>
+    <row r="9" spans="1:21" ht="14.4">
+      <c r="B9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="53" t="s">
         <v>141</v>
       </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="17" t="s">
+      <c r="D9" s="54"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="53" t="s">
         <v>142</v>
       </c>
-      <c r="G9" s="18"/>
-      <c r="H9" s="20"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="21" t="s">
+      <c r="G9" s="54"/>
+      <c r="H9" s="56"/>
+    </row>
+    <row r="10" spans="1:21" ht="14.4">
+      <c r="B10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="61" t="s">
         <v>143</v>
       </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="22" t="s">
+      <c r="D10" s="54"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="61" t="s">
         <v>144</v>
       </c>
-      <c r="G10" s="18"/>
-      <c r="H10" s="20"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="16" t="s">
+      <c r="G10" s="54"/>
+      <c r="H10" s="56"/>
+    </row>
+    <row r="11" spans="1:21" ht="14.4">
+      <c r="B11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="53" t="s">
         <v>145</v>
       </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="17" t="s">
+      <c r="D11" s="54"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="53" t="s">
         <v>146</v>
       </c>
-      <c r="G11" s="18"/>
-      <c r="H11" s="20"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="16" t="s">
+      <c r="G11" s="54"/>
+      <c r="H11" s="56"/>
+    </row>
+    <row r="12" spans="1:21" ht="14.4">
+      <c r="B12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="53" t="s">
         <v>147</v>
       </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="17" t="s">
+      <c r="D12" s="54"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="53" t="s">
         <v>148</v>
       </c>
-      <c r="G12" s="18"/>
-      <c r="H12" s="20"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="23" t="s">
+      <c r="G12" s="54"/>
+      <c r="H12" s="56"/>
+    </row>
+    <row r="13" spans="1:21" ht="14.4">
+      <c r="B13" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="57" t="s">
         <v>149</v>
       </c>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="24" t="s">
+      <c r="D13" s="58"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="57" t="s">
         <v>150</v>
       </c>
-      <c r="G13" s="25"/>
-      <c r="H13" s="27"/>
-    </row>
-    <row r="16">
+      <c r="G13" s="58"/>
+      <c r="H13" s="60"/>
+    </row>
+    <row r="16" spans="1:21" ht="13.8">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -4870,351 +3964,351 @@
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="I21" s="39" t="s">
+    <row r="21" spans="9:19" ht="15.75" customHeight="1">
+      <c r="I21" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="J21" s="40" t="s">
+      <c r="J21" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="K21" s="40" t="s">
+      <c r="K21" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="L21" s="40" t="s">
+      <c r="L21" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="M21" s="40" t="s">
+      <c r="M21" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="N21" s="40" t="s">
+      <c r="N21" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="O21" s="40" t="s">
+      <c r="O21" s="17" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="J22" s="37" t="s">
+    <row r="22" spans="9:19" ht="15.75" customHeight="1">
+      <c r="J22" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="K22" s="41" t="s">
+      <c r="K22" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="L22" s="41" t="s">
+      <c r="L22" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="M22" s="41" t="s">
+      <c r="M22" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="N22" s="42">
-        <v>3.0</v>
-      </c>
-      <c r="O22" s="41" t="s">
+      <c r="N22" s="19">
+        <v>3</v>
+      </c>
+      <c r="O22" s="18" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="J23" s="43" t="s">
+    <row r="23" spans="9:19" ht="15.75" customHeight="1">
+      <c r="J23" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="K23" s="41" t="s">
+      <c r="K23" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="L23" s="41" t="s">
+      <c r="L23" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="M23" s="41" t="s">
+      <c r="M23" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="N23" s="42">
-        <v>3.0</v>
-      </c>
-      <c r="O23" s="44" t="s">
+      <c r="N23" s="19">
+        <v>3</v>
+      </c>
+      <c r="O23" s="18" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="J24" s="45" t="s">
+    <row r="24" spans="9:19" ht="15.75" customHeight="1">
+      <c r="J24" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="K24" s="41" t="s">
+      <c r="K24" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L24" s="41" t="s">
+      <c r="L24" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="M24" s="41" t="s">
+      <c r="M24" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="N24" s="42">
-        <v>3.0</v>
-      </c>
-      <c r="O24" s="41" t="s">
+      <c r="N24" s="19">
+        <v>3</v>
+      </c>
+      <c r="O24" s="18" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="J25" s="43" t="s">
+    <row r="25" spans="9:19" ht="15.75" customHeight="1">
+      <c r="J25" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="K25" s="41" t="s">
+      <c r="K25" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="L25" s="41" t="s">
+      <c r="L25" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="M25" s="41" t="s">
+      <c r="M25" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="N25" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="O25" s="46" t="s">
+      <c r="N25" s="19">
+        <v>1</v>
+      </c>
+      <c r="O25" s="22" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="26">
-      <c r="J26" s="45" t="s">
+    <row r="26" spans="9:19" ht="41.4">
+      <c r="J26" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="K26" s="41" t="s">
+      <c r="K26" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="L26" s="41" t="s">
+      <c r="L26" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="M26" s="41" t="s">
+      <c r="M26" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="N26" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="O26" s="41" t="s">
+      <c r="N26" s="19">
+        <v>1</v>
+      </c>
+      <c r="O26" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="S26" s="47" t="s">
+      <c r="S26" s="23" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="27">
-      <c r="J27" s="45" t="s">
+    <row r="27" spans="9:19" ht="179.4">
+      <c r="J27" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="K27" s="41" t="s">
+      <c r="K27" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="L27" s="41" t="s">
+      <c r="L27" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="M27" s="41" t="s">
+      <c r="M27" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="N27" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="O27" s="41" t="s">
+      <c r="N27" s="19">
+        <v>1</v>
+      </c>
+      <c r="O27" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="S27" s="48" t="s">
+      <c r="S27" s="24" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="J28" s="49" t="s">
+    <row r="28" spans="9:19" ht="15.75" customHeight="1">
+      <c r="J28" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="K28" s="31" t="s">
+      <c r="K28" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="L28" s="31" t="s">
+      <c r="L28" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="M28" s="31" t="s">
+      <c r="M28" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="N28" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="O28" s="31" t="s">
+      <c r="N28" s="26">
+        <v>1</v>
+      </c>
+      <c r="O28" s="9" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="29" ht="36.75" customHeight="1">
-      <c r="J29" s="49" t="s">
+    <row r="29" spans="9:19" ht="36.75" customHeight="1">
+      <c r="J29" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="K29" s="31" t="s">
+      <c r="K29" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L29" s="31" t="s">
+      <c r="L29" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="M29" s="31" t="s">
+      <c r="M29" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="N29" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="O29" s="31" t="s">
+      <c r="N29" s="26">
+        <v>1</v>
+      </c>
+      <c r="O29" s="9" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="30" ht="60.0" customHeight="1">
-      <c r="J30" s="49" t="s">
+    <row r="30" spans="9:19" ht="60" customHeight="1">
+      <c r="J30" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="K30" s="31" t="s">
+      <c r="K30" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="L30" s="31" t="s">
+      <c r="L30" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="M30" s="31" t="s">
+      <c r="M30" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="N30" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="O30" s="31" t="s">
+      <c r="N30" s="26">
+        <v>1</v>
+      </c>
+      <c r="O30" s="9" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="31" ht="91.5" customHeight="1">
-      <c r="J31" s="49" t="s">
+    <row r="31" spans="9:19" ht="91.5" customHeight="1">
+      <c r="J31" s="25" t="s">
         <v>198</v>
       </c>
-      <c r="K31" s="31" t="s">
+      <c r="K31" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="L31" s="31" t="s">
+      <c r="L31" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="M31" s="31" t="s">
+      <c r="M31" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="N31" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="O31" s="31" t="s">
+      <c r="N31" s="26">
+        <v>1</v>
+      </c>
+      <c r="O31" s="9" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="32" ht="42.0" customHeight="1">
-      <c r="J32" s="49" t="s">
+    <row r="32" spans="9:19" ht="42" customHeight="1">
+      <c r="J32" s="25" t="s">
         <v>202</v>
       </c>
-      <c r="K32" s="31" t="s">
+      <c r="K32" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="L32" s="31" t="s">
+      <c r="L32" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="M32" s="31" t="s">
+      <c r="M32" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="N32" s="51"/>
-      <c r="O32" s="31" t="s">
+      <c r="N32" s="27"/>
+      <c r="O32" s="9" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="J33" s="49" t="s">
+    <row r="33" spans="1:19" ht="15.75" customHeight="1">
+      <c r="J33" s="25" t="s">
         <v>206</v>
       </c>
-      <c r="K33" s="31" t="s">
+      <c r="K33" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="L33" s="31" t="s">
+      <c r="L33" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="M33" s="31" t="s">
+      <c r="M33" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="N33" s="51">
-        <v>1.0</v>
-      </c>
-      <c r="O33" s="31" t="s">
+      <c r="N33" s="27">
+        <v>1</v>
+      </c>
+      <c r="O33" s="9" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="34" ht="67.5" customHeight="1">
-      <c r="J34" s="49" t="s">
+    <row r="34" spans="1:19" ht="67.5" customHeight="1">
+      <c r="J34" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="K34" s="31" t="s">
+      <c r="K34" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="L34" s="31" t="s">
+      <c r="L34" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="M34" s="31" t="s">
+      <c r="M34" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="N34" s="51">
-        <v>1.0</v>
-      </c>
-      <c r="O34" s="31" t="s">
+      <c r="N34" s="27">
+        <v>1</v>
+      </c>
+      <c r="O34" s="9" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="35" ht="67.5" customHeight="1">
-      <c r="J35" s="52"/>
-      <c r="K35" s="53"/>
-      <c r="L35" s="53"/>
-      <c r="M35" s="53"/>
-      <c r="N35" s="54"/>
-    </row>
-    <row r="36" ht="26.25" customHeight="1">
-      <c r="J36" s="52"/>
-      <c r="K36" s="53"/>
-      <c r="L36" s="53"/>
-      <c r="M36" s="53"/>
-      <c r="N36" s="54"/>
-    </row>
-    <row r="37" ht="24.0" customHeight="1">
-      <c r="J37" s="30" t="s">
+    <row r="35" spans="1:19" ht="67.5" customHeight="1">
+      <c r="J35" s="28"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="29"/>
+      <c r="N35" s="30"/>
+    </row>
+    <row r="36" spans="1:19" ht="26.25" customHeight="1">
+      <c r="J36" s="28"/>
+      <c r="K36" s="29"/>
+      <c r="L36" s="29"/>
+      <c r="M36" s="29"/>
+      <c r="N36" s="30"/>
+    </row>
+    <row r="37" spans="1:19" ht="24" customHeight="1">
+      <c r="J37" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="K37" s="30" t="s">
+      <c r="K37" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="L37" s="30" t="s">
+      <c r="L37" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="M37" s="30" t="s">
+      <c r="M37" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="N37" s="30" t="s">
+      <c r="N37" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="O37" s="30" t="s">
+      <c r="O37" s="8" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="I38" s="39" t="s">
+    <row r="38" spans="1:19" ht="15.75" customHeight="1">
+      <c r="I38" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="J38" s="55" t="s">
+      <c r="J38" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="K38" s="50" t="s">
+      <c r="K38" s="26" t="s">
         <v>217</v>
       </c>
-      <c r="L38" s="50" t="s">
+      <c r="L38" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="M38" s="50" t="s">
+      <c r="M38" s="26" t="s">
         <v>218</v>
       </c>
-      <c r="N38" s="50">
-        <v>3.0</v>
-      </c>
-      <c r="O38" s="50" t="s">
+      <c r="N38" s="26">
+        <v>3</v>
+      </c>
+      <c r="O38" s="26" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="39" ht="56.25" customHeight="1">
+    <row r="39" spans="1:19" ht="56.25" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -5224,22 +4318,22 @@
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
-      <c r="J39" s="43" t="s">
+      <c r="J39" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="K39" s="41" t="s">
+      <c r="K39" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="L39" s="41" t="s">
+      <c r="L39" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="M39" s="41" t="s">
+      <c r="M39" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="N39" s="42">
-        <v>3.0</v>
-      </c>
-      <c r="O39" s="44" t="s">
+      <c r="N39" s="19">
+        <v>3</v>
+      </c>
+      <c r="O39" s="18" t="s">
         <v>162</v>
       </c>
       <c r="P39" s="2"/>
@@ -5247,7 +4341,7 @@
       <c r="R39" s="2"/>
       <c r="S39" s="2"/>
     </row>
-    <row r="40" ht="52.5" customHeight="1">
+    <row r="40" spans="1:19" ht="52.5" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -5257,22 +4351,22 @@
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
-      <c r="J40" s="55" t="s">
+      <c r="J40" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="K40" s="56" t="s">
+      <c r="K40" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="L40" s="50" t="s">
+      <c r="L40" s="26" t="s">
         <v>165</v>
       </c>
-      <c r="M40" s="50" t="s">
+      <c r="M40" s="26" t="s">
         <v>221</v>
       </c>
-      <c r="N40" s="42">
-        <v>3.0</v>
-      </c>
-      <c r="O40" s="56" t="s">
+      <c r="N40" s="19">
+        <v>3</v>
+      </c>
+      <c r="O40" s="19" t="s">
         <v>222</v>
       </c>
       <c r="P40" s="2"/>
@@ -5280,7 +4374,7 @@
       <c r="R40" s="2"/>
       <c r="S40" s="2"/>
     </row>
-    <row r="41" ht="60.0" customHeight="1">
+    <row r="41" spans="1:19" ht="60" customHeight="1">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -5290,22 +4384,22 @@
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
-      <c r="J41" s="43" t="s">
+      <c r="J41" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="K41" s="41" t="s">
+      <c r="K41" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="L41" s="41" t="s">
+      <c r="L41" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="M41" s="41" t="s">
+      <c r="M41" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="N41" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="O41" s="46" t="s">
+      <c r="N41" s="19">
+        <v>1</v>
+      </c>
+      <c r="O41" s="22" t="s">
         <v>172</v>
       </c>
       <c r="P41" s="2"/>
@@ -5313,7 +4407,7 @@
       <c r="R41" s="2"/>
       <c r="S41" s="2"/>
     </row>
-    <row r="42" ht="40.5" customHeight="1">
+    <row r="42" spans="1:19" ht="40.5" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -5323,22 +4417,22 @@
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
-      <c r="J42" s="55" t="s">
+      <c r="J42" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="K42" s="50" t="s">
+      <c r="K42" s="26" t="s">
         <v>223</v>
       </c>
-      <c r="L42" s="50" t="s">
+      <c r="L42" s="26" t="s">
         <v>224</v>
       </c>
-      <c r="M42" s="50" t="s">
+      <c r="M42" s="26" t="s">
         <v>225</v>
       </c>
-      <c r="N42" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="O42" s="50" t="s">
+      <c r="N42" s="26">
+        <v>1</v>
+      </c>
+      <c r="O42" s="26" t="s">
         <v>226</v>
       </c>
       <c r="P42" s="2"/>
@@ -5346,7 +4440,7 @@
       <c r="R42" s="2"/>
       <c r="S42" s="2"/>
     </row>
-    <row r="43" ht="54.75" customHeight="1">
+    <row r="43" spans="1:19" ht="54.75" customHeight="1">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -5356,22 +4450,22 @@
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
-      <c r="J43" s="55" t="s">
+      <c r="J43" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="K43" s="50" t="s">
+      <c r="K43" s="26" t="s">
         <v>227</v>
       </c>
-      <c r="L43" s="50" t="s">
+      <c r="L43" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="M43" s="50" t="s">
+      <c r="M43" s="26" t="s">
         <v>228</v>
       </c>
-      <c r="N43" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="O43" s="50" t="s">
+      <c r="N43" s="26">
+        <v>1</v>
+      </c>
+      <c r="O43" s="26" t="s">
         <v>229</v>
       </c>
       <c r="P43" s="2"/>
@@ -5379,7 +4473,7 @@
       <c r="R43" s="2"/>
       <c r="S43" s="2"/>
     </row>
-    <row r="44" ht="50.25" customHeight="1">
+    <row r="44" spans="1:19" ht="50.25" customHeight="1">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -5389,22 +4483,22 @@
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
-      <c r="J44" s="55" t="s">
+      <c r="J44" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="K44" s="42" t="s">
+      <c r="K44" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="L44" s="50" t="s">
+      <c r="L44" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="M44" s="50" t="s">
+      <c r="M44" s="26" t="s">
         <v>231</v>
       </c>
-      <c r="N44" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="O44" s="50" t="s">
+      <c r="N44" s="26">
+        <v>1</v>
+      </c>
+      <c r="O44" s="26" t="s">
         <v>193</v>
       </c>
       <c r="P44" s="2"/>
@@ -5412,7 +4506,7 @@
       <c r="R44" s="2"/>
       <c r="S44" s="2"/>
     </row>
-    <row r="45" ht="68.25" customHeight="1">
+    <row r="45" spans="1:19" ht="68.25" customHeight="1">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -5422,22 +4516,22 @@
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
-      <c r="J45" s="55" t="s">
+      <c r="J45" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="K45" s="50" t="s">
+      <c r="K45" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="L45" s="50" t="s">
+      <c r="L45" s="26" t="s">
         <v>191</v>
       </c>
-      <c r="M45" s="50" t="s">
+      <c r="M45" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="N45" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="O45" s="50" t="s">
+      <c r="N45" s="26">
+        <v>1</v>
+      </c>
+      <c r="O45" s="26" t="s">
         <v>193</v>
       </c>
       <c r="P45" s="2"/>
@@ -5445,7 +4539,7 @@
       <c r="R45" s="2"/>
       <c r="S45" s="2"/>
     </row>
-    <row r="46" ht="51.0" customHeight="1">
+    <row r="46" spans="1:19" ht="51" customHeight="1">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -5455,22 +4549,22 @@
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
-      <c r="J46" s="55" t="s">
+      <c r="J46" s="31" t="s">
         <v>194</v>
       </c>
-      <c r="K46" s="50" t="s">
+      <c r="K46" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="L46" s="50" t="s">
+      <c r="L46" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="M46" s="50" t="s">
+      <c r="M46" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="N46" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="O46" s="50" t="s">
+      <c r="N46" s="26">
+        <v>1</v>
+      </c>
+      <c r="O46" s="26" t="s">
         <v>193</v>
       </c>
       <c r="P46" s="2"/>
@@ -5478,7 +4572,7 @@
       <c r="R46" s="2"/>
       <c r="S46" s="2"/>
     </row>
-    <row r="47" ht="44.25" customHeight="1">
+    <row r="47" spans="1:19" ht="44.25" customHeight="1">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -5488,22 +4582,22 @@
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
-      <c r="J47" s="55" t="s">
+      <c r="J47" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="K47" s="50" t="s">
+      <c r="K47" s="26" t="s">
         <v>237</v>
       </c>
-      <c r="L47" s="50" t="s">
+      <c r="L47" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="M47" s="50" t="s">
+      <c r="M47" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="N47" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="O47" s="50" t="s">
+      <c r="N47" s="26">
+        <v>1</v>
+      </c>
+      <c r="O47" s="26" t="s">
         <v>193</v>
       </c>
       <c r="P47" s="2"/>
@@ -5511,7 +4605,7 @@
       <c r="R47" s="2"/>
       <c r="S47" s="2"/>
     </row>
-    <row r="48" ht="66.75" customHeight="1">
+    <row r="48" spans="1:19" ht="66.75" customHeight="1">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -5521,22 +4615,22 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
-      <c r="J48" s="55" t="s">
+      <c r="J48" s="31" t="s">
         <v>202</v>
       </c>
-      <c r="K48" s="50" t="s">
+      <c r="K48" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="L48" s="50" t="s">
+      <c r="L48" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="M48" s="50" t="s">
+      <c r="M48" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="N48" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="O48" s="50" t="s">
+      <c r="N48" s="26">
+        <v>1</v>
+      </c>
+      <c r="O48" s="26" t="s">
         <v>193</v>
       </c>
       <c r="P48" s="2"/>
@@ -5544,7 +4638,7 @@
       <c r="R48" s="2"/>
       <c r="S48" s="2"/>
     </row>
-    <row r="49" ht="41.25" customHeight="1">
+    <row r="49" spans="1:19" ht="41.25" customHeight="1">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -5554,22 +4648,22 @@
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
-      <c r="J49" s="55" t="s">
+      <c r="J49" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="K49" s="50" t="s">
+      <c r="K49" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="L49" s="50" t="s">
+      <c r="L49" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="M49" s="50" t="s">
+      <c r="M49" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="N49" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="O49" s="50" t="s">
+      <c r="N49" s="26">
+        <v>1</v>
+      </c>
+      <c r="O49" s="26" t="s">
         <v>243</v>
       </c>
       <c r="P49" s="2"/>
@@ -5577,7 +4671,7 @@
       <c r="R49" s="2"/>
       <c r="S49" s="2"/>
     </row>
-    <row r="50" ht="55.5" customHeight="1">
+    <row r="50" spans="1:19" ht="55.5" customHeight="1">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -5587,22 +4681,22 @@
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
-      <c r="J50" s="57" t="s">
+      <c r="J50" s="32" t="s">
         <v>211</v>
       </c>
-      <c r="K50" s="50" t="s">
+      <c r="K50" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="L50" s="50" t="s">
+      <c r="L50" s="26" t="s">
         <v>213</v>
       </c>
-      <c r="M50" s="50" t="s">
+      <c r="M50" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="N50" s="51">
-        <v>1.0</v>
-      </c>
-      <c r="O50" s="58" t="s">
+      <c r="N50" s="27">
+        <v>1</v>
+      </c>
+      <c r="O50" s="33" t="s">
         <v>246</v>
       </c>
       <c r="P50" s="2"/>
@@ -5610,7 +4704,7 @@
       <c r="R50" s="2"/>
       <c r="S50" s="2"/>
     </row>
-    <row r="51" ht="43.5" customHeight="1">
+    <row r="51" spans="1:19" ht="43.5" customHeight="1">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -5631,7 +4725,7 @@
       <c r="R51" s="2"/>
       <c r="S51" s="2"/>
     </row>
-    <row r="52" ht="48.75" customHeight="1">
+    <row r="52" spans="1:19" ht="48.75" customHeight="1">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -5652,7 +4746,7 @@
       <c r="R52" s="2"/>
       <c r="S52" s="2"/>
     </row>
-    <row r="53" ht="30.75" customHeight="1">
+    <row r="53" spans="1:19" ht="30.75" customHeight="1">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -5662,22 +4756,22 @@
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
-      <c r="J53" s="30" t="s">
+      <c r="J53" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="K53" s="30" t="s">
+      <c r="K53" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="L53" s="30" t="s">
+      <c r="L53" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="M53" s="30" t="s">
+      <c r="M53" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="N53" s="30" t="s">
+      <c r="N53" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="O53" s="30" t="s">
+      <c r="O53" s="8" t="s">
         <v>216</v>
       </c>
       <c r="P53" s="2"/>
@@ -5685,7 +4779,7 @@
       <c r="R53" s="2"/>
       <c r="S53" s="2"/>
     </row>
-    <row r="54" ht="29.25" customHeight="1">
+    <row r="54" spans="1:19" ht="29.25" customHeight="1">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -5695,22 +4789,22 @@
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
-      <c r="J54" s="49" t="s">
+      <c r="J54" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="K54" s="44" t="s">
+      <c r="K54" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="L54" s="31" t="s">
+      <c r="L54" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="M54" s="31" t="s">
+      <c r="M54" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="N54" s="50">
-        <v>3.0</v>
-      </c>
-      <c r="O54" s="31" t="s">
+      <c r="N54" s="26">
+        <v>3</v>
+      </c>
+      <c r="O54" s="9" t="s">
         <v>249</v>
       </c>
       <c r="P54" s="2"/>
@@ -5718,7 +4812,7 @@
       <c r="R54" s="2"/>
       <c r="S54" s="2"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:19" ht="55.2">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -5727,25 +4821,25 @@
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
-      <c r="I55" s="39" t="s">
+      <c r="I55" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="J55" s="43" t="s">
+      <c r="J55" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="K55" s="41" t="s">
+      <c r="K55" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="L55" s="41" t="s">
+      <c r="L55" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="M55" s="41" t="s">
+      <c r="M55" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="N55" s="42">
-        <v>3.0</v>
-      </c>
-      <c r="O55" s="44" t="s">
+      <c r="N55" s="19">
+        <v>3</v>
+      </c>
+      <c r="O55" s="18" t="s">
         <v>162</v>
       </c>
       <c r="P55" s="2"/>
@@ -5753,7 +4847,7 @@
       <c r="R55" s="2"/>
       <c r="S55" s="2"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:19" ht="27.6">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -5763,22 +4857,22 @@
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
-      <c r="J56" s="49" t="s">
+      <c r="J56" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="K56" s="31" t="s">
+      <c r="K56" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="L56" s="31" t="s">
+      <c r="L56" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="M56" s="31" t="s">
+      <c r="M56" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="N56" s="42">
-        <v>3.0</v>
-      </c>
-      <c r="O56" s="31" t="s">
+      <c r="N56" s="19">
+        <v>3</v>
+      </c>
+      <c r="O56" s="9" t="s">
         <v>252</v>
       </c>
       <c r="P56" s="2"/>
@@ -5786,7 +4880,7 @@
       <c r="R56" s="2"/>
       <c r="S56" s="2"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:19" ht="41.4">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -5796,22 +4890,22 @@
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
-      <c r="J57" s="43" t="s">
+      <c r="J57" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="K57" s="41" t="s">
+      <c r="K57" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="L57" s="41" t="s">
+      <c r="L57" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="M57" s="41" t="s">
+      <c r="M57" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="N57" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="O57" s="46" t="s">
+      <c r="N57" s="19">
+        <v>1</v>
+      </c>
+      <c r="O57" s="22" t="s">
         <v>172</v>
       </c>
       <c r="P57" s="2"/>
@@ -5819,27 +4913,27 @@
       <c r="R57" s="2"/>
       <c r="S57" s="2"/>
     </row>
-    <row r="58">
-      <c r="J58" s="49" t="s">
+    <row r="58" spans="1:19" ht="27.6">
+      <c r="J58" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="K58" s="31" t="s">
+      <c r="K58" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="L58" s="31" t="s">
+      <c r="L58" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="M58" s="31" t="s">
+      <c r="M58" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="N58" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="O58" s="44" t="s">
+      <c r="N58" s="26">
+        <v>1</v>
+      </c>
+      <c r="O58" s="18" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:19" ht="27.6">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -5849,22 +4943,22 @@
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
-      <c r="J59" s="49" t="s">
+      <c r="J59" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="K59" s="31" t="s">
+      <c r="K59" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="L59" s="31" t="s">
+      <c r="L59" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="M59" s="44" t="s">
+      <c r="M59" s="18" t="s">
         <v>257</v>
       </c>
-      <c r="N59" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="O59" s="44" t="s">
+      <c r="N59" s="26">
+        <v>1</v>
+      </c>
+      <c r="O59" s="18" t="s">
         <v>258</v>
       </c>
       <c r="P59" s="2"/>
@@ -5872,7 +4966,7 @@
       <c r="R59" s="2"/>
       <c r="S59" s="2"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:19" ht="15.75" customHeight="1">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -5882,22 +4976,22 @@
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
-      <c r="J60" s="49" t="s">
+      <c r="J60" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="K60" s="31" t="s">
+      <c r="K60" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="L60" s="31" t="s">
+      <c r="L60" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="M60" s="31" t="s">
+      <c r="M60" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="N60" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="O60" s="31" t="s">
+      <c r="N60" s="26">
+        <v>1</v>
+      </c>
+      <c r="O60" s="9" t="s">
         <v>261</v>
       </c>
       <c r="P60" s="2"/>
@@ -5905,7 +4999,7 @@
       <c r="R60" s="2"/>
       <c r="S60" s="2"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:19" ht="15.75" customHeight="1">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -5915,22 +5009,22 @@
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
-      <c r="J61" s="49" t="s">
+      <c r="J61" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="K61" s="31" t="s">
+      <c r="K61" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="L61" s="31" t="s">
+      <c r="L61" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="M61" s="31" t="s">
+      <c r="M61" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="N61" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="O61" s="31" t="s">
+      <c r="N61" s="26">
+        <v>1</v>
+      </c>
+      <c r="O61" s="9" t="s">
         <v>193</v>
       </c>
       <c r="P61" s="2"/>
@@ -5938,7 +5032,7 @@
       <c r="R61" s="2"/>
       <c r="S61" s="2"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="1:19" ht="15.75" customHeight="1">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -5948,22 +5042,22 @@
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
-      <c r="J62" s="49" t="s">
+      <c r="J62" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="K62" s="31" t="s">
+      <c r="K62" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="L62" s="31" t="s">
+      <c r="L62" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="M62" s="31" t="s">
+      <c r="M62" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="N62" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="O62" s="31" t="s">
+      <c r="N62" s="26">
+        <v>1</v>
+      </c>
+      <c r="O62" s="9" t="s">
         <v>193</v>
       </c>
       <c r="P62" s="2"/>
@@ -5971,7 +5065,7 @@
       <c r="R62" s="2"/>
       <c r="S62" s="2"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="1:19" ht="15.75" customHeight="1">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -5981,22 +5075,22 @@
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
-      <c r="J63" s="49" t="s">
+      <c r="J63" s="25" t="s">
         <v>198</v>
       </c>
-      <c r="K63" s="31" t="s">
+      <c r="K63" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="L63" s="31" t="s">
+      <c r="L63" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="M63" s="31" t="s">
+      <c r="M63" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="N63" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="O63" s="31" t="s">
+      <c r="N63" s="26">
+        <v>1</v>
+      </c>
+      <c r="O63" s="9" t="s">
         <v>193</v>
       </c>
       <c r="P63" s="2"/>
@@ -6004,7 +5098,7 @@
       <c r="R63" s="2"/>
       <c r="S63" s="2"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="1:19" ht="15.75" customHeight="1">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -6014,22 +5108,22 @@
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
-      <c r="J64" s="49" t="s">
+      <c r="J64" s="25" t="s">
         <v>202</v>
       </c>
-      <c r="K64" s="31" t="s">
+      <c r="K64" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="L64" s="31" t="s">
+      <c r="L64" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="M64" s="31" t="s">
+      <c r="M64" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="N64" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="O64" s="31" t="s">
+      <c r="N64" s="26">
+        <v>1</v>
+      </c>
+      <c r="O64" s="9" t="s">
         <v>271</v>
       </c>
       <c r="P64" s="2"/>
@@ -6037,7 +5131,7 @@
       <c r="R64" s="2"/>
       <c r="S64" s="2"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="1:20" ht="15.75" customHeight="1">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -6047,22 +5141,22 @@
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
-      <c r="J65" s="49" t="s">
+      <c r="J65" s="25" t="s">
         <v>206</v>
       </c>
-      <c r="K65" s="31" t="s">
+      <c r="K65" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="L65" s="31" t="s">
+      <c r="L65" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="M65" s="31" t="s">
+      <c r="M65" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="N65" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="O65" s="31" t="s">
+      <c r="N65" s="26">
+        <v>1</v>
+      </c>
+      <c r="O65" s="9" t="s">
         <v>274</v>
       </c>
       <c r="P65" s="2"/>
@@ -6070,7 +5164,7 @@
       <c r="R65" s="2"/>
       <c r="S65" s="2"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="1:20" ht="15.75" customHeight="1">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -6080,22 +5174,22 @@
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
-      <c r="J66" s="49" t="s">
+      <c r="J66" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="K66" s="31" t="s">
+      <c r="K66" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="L66" s="31" t="s">
+      <c r="L66" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="M66" s="31" t="s">
+      <c r="M66" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="N66" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="O66" s="31" t="s">
+      <c r="N66" s="26">
+        <v>1</v>
+      </c>
+      <c r="O66" s="9" t="s">
         <v>277</v>
       </c>
       <c r="P66" s="2"/>
@@ -6103,7 +5197,7 @@
       <c r="R66" s="2"/>
       <c r="S66" s="2"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="1:20" ht="15.75" customHeight="1">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -6124,7 +5218,7 @@
       <c r="R67" s="2"/>
       <c r="S67" s="2"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" spans="1:20" ht="15.75" customHeight="1">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -6145,7 +5239,7 @@
       <c r="R68" s="2"/>
       <c r="S68" s="2"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" spans="1:20" ht="15.75" customHeight="1">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -6166,7 +5260,7 @@
       <c r="R69" s="2"/>
       <c r="S69" s="2"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" spans="1:20" ht="15.75" customHeight="1">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -6181,7 +5275,7 @@
       <c r="R70" s="2"/>
       <c r="S70" s="2"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="1:20" ht="15.75" customHeight="1">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -6202,7 +5296,7 @@
       <c r="R71" s="2"/>
       <c r="S71" s="2"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" spans="1:20" ht="15.75" customHeight="1">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -6217,8 +5311,8 @@
       <c r="R72" s="2"/>
       <c r="S72" s="2"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="73" spans="1:20" ht="15.75" customHeight="1"/>
+    <row r="74" spans="1:20" ht="15.75" customHeight="1">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -6228,131 +5322,131 @@
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
-      <c r="K74" s="33" t="s">
+      <c r="K74" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="L74" s="33"/>
+      <c r="L74" s="11"/>
       <c r="P74" s="1"/>
       <c r="Q74" s="1"/>
       <c r="R74" s="1"/>
       <c r="S74" s="1"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="K75" s="36" t="s">
+    <row r="75" spans="1:20" ht="15.75" customHeight="1">
+      <c r="K75" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="L75" s="36" t="s">
+      <c r="L75" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="M75" s="36" t="s">
+      <c r="M75" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="N75" s="36" t="s">
+      <c r="N75" s="13" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="K76" s="37" t="s">
+    <row r="76" spans="1:20" ht="15.75" customHeight="1">
+      <c r="K76" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="L76" s="38" t="s">
+      <c r="L76" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="M76" s="38" t="s">
+      <c r="M76" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="N76" s="38" t="s">
+      <c r="N76" s="15" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="K77" s="37" t="s">
+    <row r="77" spans="1:20" ht="15.75" customHeight="1">
+      <c r="K77" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="L77" s="38" t="s">
+      <c r="L77" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="M77" s="38" t="s">
+      <c r="M77" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="N77" s="38" t="s">
+      <c r="N77" s="15" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="78" ht="39.75" customHeight="1">
-      <c r="K78" s="37" t="s">
+    <row r="78" spans="1:20" ht="39.75" customHeight="1">
+      <c r="K78" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="L78" s="38" t="s">
+      <c r="L78" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="M78" s="38" t="s">
+      <c r="M78" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="N78" s="38" t="s">
+      <c r="N78" s="15" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="79" ht="51.0" customHeight="1">
-      <c r="K79" s="37" t="s">
+    <row r="79" spans="1:20" ht="51" customHeight="1">
+      <c r="K79" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="L79" s="38" t="s">
+      <c r="L79" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="M79" s="38" t="s">
+      <c r="M79" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="N79" s="38" t="s">
+      <c r="N79" s="15" t="s">
         <v>295</v>
       </c>
       <c r="T79" s="2"/>
     </row>
-    <row r="80" ht="70.5" customHeight="1">
-      <c r="K80" s="37" t="s">
+    <row r="80" spans="1:20" ht="70.5" customHeight="1">
+      <c r="K80" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="L80" s="38" t="s">
+      <c r="L80" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="M80" s="38" t="s">
+      <c r="M80" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="N80" s="38" t="s">
+      <c r="N80" s="15" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="81" ht="46.5" customHeight="1">
-      <c r="K81" s="37" t="s">
+    <row r="81" spans="2:19" ht="46.5" customHeight="1">
+      <c r="K81" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="L81" s="38" t="s">
+      <c r="L81" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="M81" s="38" t="s">
+      <c r="M81" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="N81" s="38" t="s">
+      <c r="N81" s="15" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="82" ht="40.5" customHeight="1">
-      <c r="K82" s="37" t="s">
+    <row r="82" spans="2:19" ht="40.5" customHeight="1">
+      <c r="K82" s="14" t="s">
         <v>302</v>
       </c>
-      <c r="L82" s="38" t="s">
+      <c r="L82" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="M82" s="38" t="s">
+      <c r="M82" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="N82" s="38" t="s">
+      <c r="N82" s="15" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="83" ht="40.5" customHeight="1"/>
-    <row r="84" ht="45.0" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="83" spans="2:19" ht="40.5" customHeight="1"/>
+    <row r="84" spans="2:19" ht="45" customHeight="1"/>
+    <row r="85" spans="2:19" ht="15.75" customHeight="1">
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
@@ -6360,9 +5454,9 @@
       <c r="N85" s="1"/>
       <c r="O85" s="1"/>
     </row>
-    <row r="86" ht="30.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="86" spans="2:19" ht="30.75" customHeight="1"/>
+    <row r="87" spans="2:19" ht="15.75" customHeight="1"/>
+    <row r="88" spans="2:19" ht="15.75" customHeight="1">
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
@@ -6376,14 +5470,14 @@
       <c r="R88" s="1"/>
       <c r="S88" s="1"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="89" spans="2:19" ht="15.75" customHeight="1"/>
+    <row r="90" spans="2:19" ht="15.75" customHeight="1"/>
+    <row r="91" spans="2:19" ht="15.75" customHeight="1"/>
+    <row r="92" spans="2:19" ht="15.75" customHeight="1"/>
+    <row r="93" spans="2:19" ht="15.75" customHeight="1"/>
+    <row r="94" spans="2:19" ht="15.75" customHeight="1"/>
+    <row r="95" spans="2:19" ht="15.75" customHeight="1"/>
+    <row r="96" spans="2:19" ht="15.75" customHeight="1"/>
     <row r="97" ht="15.75" customHeight="1"/>
     <row r="98" ht="15.75" customHeight="1"/>
     <row r="99" ht="15.75" customHeight="1"/>
@@ -7290,12 +6384,6 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:E6"/>
-    <mergeCell ref="F5:H6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="F7:H7"/>
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="C12:E12"/>
     <mergeCell ref="F12:H12"/>
@@ -7308,32 +6396,34 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="F11:H11"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:E6"/>
+    <mergeCell ref="F5:H6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F7:H7"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:AB938"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.63"/>
-    <col customWidth="1" min="2" max="2" width="28.13"/>
-    <col customWidth="1" min="3" max="3" width="33.13"/>
-    <col customWidth="1" min="4" max="4" width="21.75"/>
-    <col customWidth="1" min="5" max="5" width="15.13"/>
-    <col customWidth="1" min="6" max="6" width="16.63"/>
-    <col customWidth="1" min="7" max="7" width="13.63"/>
-    <col customWidth="1" min="8" max="28" width="10.63"/>
+    <col min="1" max="1" width="10.59765625" customWidth="1"/>
+    <col min="2" max="2" width="28.09765625" customWidth="1"/>
+    <col min="3" max="3" width="33.09765625" customWidth="1"/>
+    <col min="4" max="4" width="21.69921875" customWidth="1"/>
+    <col min="5" max="5" width="15.09765625" customWidth="1"/>
+    <col min="6" max="6" width="16.59765625" customWidth="1"/>
+    <col min="7" max="7" width="13.59765625" customWidth="1"/>
+    <col min="8" max="28" width="10.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:28" ht="13.8">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7363,92 +6453,92 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="4">
-      <c r="B4" s="59" t="s">
+    <row r="4" spans="1:28" ht="28.8">
+      <c r="B4" s="34" t="s">
         <v>305</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="13" t="s">
         <v>306</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="D4" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="13" t="s">
         <v>308</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="G4" s="60" t="s">
+      <c r="G4" s="35" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="61" t="s">
+    <row r="5" spans="1:28" ht="43.2">
+      <c r="B5" s="36" t="s">
         <v>311</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="E5" s="38" t="s">
+      <c r="E5" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="F5" s="38" t="s">
+      <c r="F5" s="15" t="s">
         <v>315</v>
       </c>
-      <c r="G5" s="62" t="s">
+      <c r="G5" s="37" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="63" t="s">
+    <row r="6" spans="1:28" ht="86.4">
+      <c r="B6" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="C6" s="37" t="s">
+      <c r="C6" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="E6" s="38" t="s">
+      <c r="E6" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="F6" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="G6" s="62" t="s">
+      <c r="G6" s="37" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="61" t="s">
+    <row r="7" spans="1:28" ht="86.4">
+      <c r="B7" s="36" t="s">
         <v>322</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="E7" s="38" t="s">
+      <c r="E7" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="G7" s="62" t="s">
+      <c r="G7" s="37" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="8" ht="23.25" customHeight="1">
-      <c r="C8" s="64" t="s">
+    <row r="8" spans="1:28" ht="23.25" customHeight="1">
+      <c r="C8" s="39" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:28" ht="13.8">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -7478,923 +6568,71 @@
       <c r="AA10" s="1"/>
       <c r="AB10" s="1"/>
     </row>
-    <row r="19">
-      <c r="B19" s="65" t="s">
-        <v>325</v>
-      </c>
-      <c r="C19" s="66"/>
-      <c r="D19" s="67" t="s">
-        <v>326</v>
-      </c>
-      <c r="E19" s="68"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="69"/>
-      <c r="H19" s="70" t="s">
-        <v>327</v>
-      </c>
-      <c r="I19" s="68"/>
-      <c r="J19" s="68"/>
-      <c r="K19" s="69"/>
-      <c r="L19" s="71" t="s">
-        <v>328</v>
-      </c>
-      <c r="M19" s="68"/>
-      <c r="N19" s="68"/>
-      <c r="O19" s="69"/>
-      <c r="P19" s="72" t="s">
-        <v>329</v>
-      </c>
-      <c r="Q19" s="68"/>
-      <c r="R19" s="68"/>
-      <c r="S19" s="69"/>
-      <c r="T19" s="73" t="s">
-        <v>330</v>
-      </c>
-      <c r="U19" s="68"/>
-      <c r="V19" s="68"/>
-      <c r="W19" s="69"/>
-      <c r="X19" s="74" t="s">
-        <v>331</v>
-      </c>
-      <c r="Y19" s="68"/>
-      <c r="Z19" s="68"/>
-      <c r="AA19" s="69"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="75"/>
-      <c r="C20" s="76"/>
-      <c r="D20" s="77" t="s">
-        <v>332</v>
-      </c>
-      <c r="E20" s="78" t="s">
-        <v>333</v>
-      </c>
-      <c r="F20" s="78" t="s">
-        <v>334</v>
-      </c>
-      <c r="G20" s="79" t="s">
-        <v>335</v>
-      </c>
-      <c r="H20" s="80" t="s">
-        <v>332</v>
-      </c>
-      <c r="I20" s="81" t="s">
-        <v>333</v>
-      </c>
-      <c r="J20" s="81" t="s">
-        <v>334</v>
-      </c>
-      <c r="K20" s="82" t="s">
-        <v>335</v>
-      </c>
-      <c r="L20" s="83" t="s">
-        <v>332</v>
-      </c>
-      <c r="M20" s="84" t="s">
-        <v>333</v>
-      </c>
-      <c r="N20" s="84" t="s">
-        <v>334</v>
-      </c>
-      <c r="O20" s="85" t="s">
-        <v>335</v>
-      </c>
-      <c r="P20" s="86" t="s">
-        <v>332</v>
-      </c>
-      <c r="Q20" s="87" t="s">
-        <v>333</v>
-      </c>
-      <c r="R20" s="87" t="s">
-        <v>334</v>
-      </c>
-      <c r="S20" s="88" t="s">
-        <v>335</v>
-      </c>
-      <c r="T20" s="89" t="s">
-        <v>332</v>
-      </c>
-      <c r="U20" s="90" t="s">
-        <v>333</v>
-      </c>
-      <c r="V20" s="90" t="s">
-        <v>334</v>
-      </c>
-      <c r="W20" s="91" t="s">
-        <v>335</v>
-      </c>
-      <c r="X20" s="92" t="s">
-        <v>332</v>
-      </c>
-      <c r="Y20" s="93" t="s">
-        <v>333</v>
-      </c>
-      <c r="Z20" s="93" t="s">
-        <v>334</v>
-      </c>
-      <c r="AA20" s="94" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="B21" s="95" t="s">
-        <v>336</v>
-      </c>
-      <c r="C21" s="96" t="s">
-        <v>337</v>
-      </c>
-      <c r="D21" s="97"/>
-      <c r="E21" s="98"/>
-      <c r="F21" s="98"/>
-      <c r="G21" s="99"/>
-      <c r="H21" s="100"/>
-      <c r="I21" s="98"/>
-      <c r="J21" s="98"/>
-      <c r="K21" s="99"/>
-      <c r="L21" s="100"/>
-      <c r="M21" s="98"/>
-      <c r="N21" s="98"/>
-      <c r="O21" s="99"/>
-      <c r="P21" s="100"/>
-      <c r="Q21" s="98"/>
-      <c r="R21" s="98"/>
-      <c r="S21" s="99"/>
-      <c r="T21" s="100"/>
-      <c r="U21" s="98"/>
-      <c r="V21" s="98"/>
-      <c r="W21" s="99"/>
-      <c r="X21" s="100"/>
-      <c r="Y21" s="98"/>
-      <c r="Z21" s="98"/>
-      <c r="AA21" s="99"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="B22" s="101" t="s">
-        <v>338</v>
-      </c>
-      <c r="C22" s="102" t="s">
-        <v>339</v>
-      </c>
-      <c r="D22" s="103"/>
-      <c r="E22" s="104"/>
-      <c r="F22" s="104"/>
-      <c r="G22" s="105"/>
-      <c r="H22" s="106"/>
-      <c r="I22" s="104"/>
-      <c r="J22" s="104"/>
-      <c r="K22" s="105"/>
-      <c r="L22" s="106"/>
-      <c r="M22" s="104"/>
-      <c r="N22" s="104"/>
-      <c r="O22" s="105"/>
-      <c r="P22" s="106"/>
-      <c r="Q22" s="104"/>
-      <c r="R22" s="104"/>
-      <c r="S22" s="105"/>
-      <c r="T22" s="106"/>
-      <c r="U22" s="104"/>
-      <c r="V22" s="104"/>
-      <c r="W22" s="105"/>
-      <c r="X22" s="106"/>
-      <c r="Y22" s="104"/>
-      <c r="Z22" s="104"/>
-      <c r="AA22" s="105"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="B23" s="107"/>
-      <c r="C23" s="102" t="s">
-        <v>340</v>
-      </c>
-      <c r="D23" s="106"/>
-      <c r="E23" s="108"/>
-      <c r="F23" s="104"/>
-      <c r="G23" s="105"/>
-      <c r="H23" s="106"/>
-      <c r="I23" s="104"/>
-      <c r="J23" s="104"/>
-      <c r="K23" s="105"/>
-      <c r="L23" s="106"/>
-      <c r="M23" s="104"/>
-      <c r="N23" s="104"/>
-      <c r="O23" s="105"/>
-      <c r="P23" s="106"/>
-      <c r="Q23" s="104"/>
-      <c r="R23" s="104"/>
-      <c r="S23" s="105"/>
-      <c r="T23" s="106"/>
-      <c r="U23" s="104"/>
-      <c r="V23" s="104"/>
-      <c r="W23" s="105"/>
-      <c r="X23" s="106"/>
-      <c r="Y23" s="104"/>
-      <c r="Z23" s="104"/>
-      <c r="AA23" s="105"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="B24" s="109"/>
-      <c r="C24" s="110" t="s">
-        <v>341</v>
-      </c>
-      <c r="D24" s="111"/>
-      <c r="E24" s="112"/>
-      <c r="F24" s="113"/>
-      <c r="G24" s="114"/>
-      <c r="H24" s="111"/>
-      <c r="I24" s="115"/>
-      <c r="J24" s="115"/>
-      <c r="K24" s="116"/>
-      <c r="L24" s="111"/>
-      <c r="M24" s="115"/>
-      <c r="N24" s="115"/>
-      <c r="O24" s="116"/>
-      <c r="P24" s="111"/>
-      <c r="Q24" s="115"/>
-      <c r="R24" s="115"/>
-      <c r="S24" s="116"/>
-      <c r="T24" s="111"/>
-      <c r="U24" s="115"/>
-      <c r="V24" s="115"/>
-      <c r="W24" s="116"/>
-      <c r="X24" s="111"/>
-      <c r="Y24" s="115"/>
-      <c r="Z24" s="115"/>
-      <c r="AA24" s="116"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="B25" s="117" t="s">
-        <v>342</v>
-      </c>
-      <c r="C25" s="118" t="s">
-        <v>343</v>
-      </c>
-      <c r="D25" s="119"/>
-      <c r="E25" s="120"/>
-      <c r="F25" s="120"/>
-      <c r="G25" s="121"/>
-      <c r="H25" s="122"/>
-      <c r="I25" s="120"/>
-      <c r="J25" s="120"/>
-      <c r="K25" s="123"/>
-      <c r="L25" s="119"/>
-      <c r="M25" s="120"/>
-      <c r="N25" s="120"/>
-      <c r="O25" s="123"/>
-      <c r="P25" s="119"/>
-      <c r="Q25" s="120"/>
-      <c r="R25" s="120"/>
-      <c r="S25" s="123"/>
-      <c r="T25" s="119"/>
-      <c r="U25" s="120"/>
-      <c r="V25" s="120"/>
-      <c r="W25" s="123"/>
-      <c r="X25" s="119"/>
-      <c r="Y25" s="120"/>
-      <c r="Z25" s="120"/>
-      <c r="AA25" s="123"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="B26" s="107"/>
-      <c r="C26" s="102" t="s">
-        <v>344</v>
-      </c>
-      <c r="D26" s="106"/>
-      <c r="E26" s="104"/>
-      <c r="F26" s="104"/>
-      <c r="G26" s="105"/>
-      <c r="H26" s="106"/>
-      <c r="I26" s="124"/>
-      <c r="J26" s="104"/>
-      <c r="K26" s="105"/>
-      <c r="L26" s="106"/>
-      <c r="M26" s="104"/>
-      <c r="N26" s="104"/>
-      <c r="O26" s="105"/>
-      <c r="P26" s="106"/>
-      <c r="Q26" s="104"/>
-      <c r="R26" s="104"/>
-      <c r="S26" s="105"/>
-      <c r="T26" s="106"/>
-      <c r="U26" s="104"/>
-      <c r="V26" s="104"/>
-      <c r="W26" s="105"/>
-      <c r="X26" s="106"/>
-      <c r="Y26" s="104"/>
-      <c r="Z26" s="104"/>
-      <c r="AA26" s="105"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="B27" s="125"/>
-      <c r="C27" s="126" t="s">
-        <v>345</v>
-      </c>
-      <c r="D27" s="127"/>
-      <c r="E27" s="128"/>
-      <c r="F27" s="128"/>
-      <c r="G27" s="129"/>
-      <c r="H27" s="127"/>
-      <c r="I27" s="128"/>
-      <c r="J27" s="130"/>
-      <c r="K27" s="131"/>
-      <c r="L27" s="127"/>
-      <c r="M27" s="128"/>
-      <c r="N27" s="128"/>
-      <c r="O27" s="129"/>
-      <c r="P27" s="127"/>
-      <c r="Q27" s="128"/>
-      <c r="R27" s="128"/>
-      <c r="S27" s="129"/>
-      <c r="T27" s="127"/>
-      <c r="U27" s="128"/>
-      <c r="V27" s="128"/>
-      <c r="W27" s="129"/>
-      <c r="X27" s="127"/>
-      <c r="Y27" s="128"/>
-      <c r="Z27" s="128"/>
-      <c r="AA27" s="129"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="B28" s="132" t="s">
-        <v>346</v>
-      </c>
-      <c r="C28" s="133" t="s">
-        <v>347</v>
-      </c>
-      <c r="D28" s="134"/>
-      <c r="E28" s="135"/>
-      <c r="F28" s="135"/>
-      <c r="G28" s="136"/>
-      <c r="H28" s="134"/>
-      <c r="I28" s="135"/>
-      <c r="J28" s="135"/>
-      <c r="K28" s="137"/>
-      <c r="L28" s="138"/>
-      <c r="M28" s="135"/>
-      <c r="N28" s="135"/>
-      <c r="O28" s="136"/>
-      <c r="P28" s="134"/>
-      <c r="Q28" s="135"/>
-      <c r="R28" s="135"/>
-      <c r="S28" s="136"/>
-      <c r="T28" s="134"/>
-      <c r="U28" s="135"/>
-      <c r="V28" s="135"/>
-      <c r="W28" s="136"/>
-      <c r="X28" s="134"/>
-      <c r="Y28" s="135"/>
-      <c r="Z28" s="135"/>
-      <c r="AA28" s="136"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="B29" s="107"/>
-      <c r="C29" s="102" t="s">
-        <v>348</v>
-      </c>
-      <c r="D29" s="106"/>
-      <c r="E29" s="104"/>
-      <c r="F29" s="104"/>
-      <c r="G29" s="105"/>
-      <c r="H29" s="106"/>
-      <c r="I29" s="104"/>
-      <c r="J29" s="104"/>
-      <c r="K29" s="105"/>
-      <c r="L29" s="106"/>
-      <c r="M29" s="139"/>
-      <c r="N29" s="104"/>
-      <c r="O29" s="105"/>
-      <c r="P29" s="106"/>
-      <c r="Q29" s="104"/>
-      <c r="R29" s="104"/>
-      <c r="S29" s="105"/>
-      <c r="T29" s="106"/>
-      <c r="U29" s="104"/>
-      <c r="V29" s="104"/>
-      <c r="W29" s="105"/>
-      <c r="X29" s="106"/>
-      <c r="Y29" s="104"/>
-      <c r="Z29" s="104"/>
-      <c r="AA29" s="105"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="B30" s="125"/>
-      <c r="C30" s="126" t="s">
-        <v>349</v>
-      </c>
-      <c r="D30" s="127"/>
-      <c r="E30" s="128"/>
-      <c r="F30" s="128"/>
-      <c r="G30" s="129"/>
-      <c r="H30" s="127"/>
-      <c r="I30" s="128"/>
-      <c r="J30" s="128"/>
-      <c r="K30" s="129"/>
-      <c r="L30" s="127"/>
-      <c r="M30" s="128"/>
-      <c r="N30" s="140"/>
-      <c r="O30" s="141"/>
-      <c r="P30" s="127"/>
-      <c r="Q30" s="128"/>
-      <c r="R30" s="128"/>
-      <c r="S30" s="129"/>
-      <c r="T30" s="127"/>
-      <c r="U30" s="128"/>
-      <c r="V30" s="128"/>
-      <c r="W30" s="129"/>
-      <c r="X30" s="127"/>
-      <c r="Y30" s="128"/>
-      <c r="Z30" s="128"/>
-      <c r="AA30" s="129"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="B31" s="132" t="s">
-        <v>350</v>
-      </c>
-      <c r="C31" s="133" t="s">
-        <v>351</v>
-      </c>
-      <c r="D31" s="134"/>
-      <c r="E31" s="135"/>
-      <c r="F31" s="135"/>
-      <c r="G31" s="136"/>
-      <c r="H31" s="134"/>
-      <c r="I31" s="135"/>
-      <c r="J31" s="135"/>
-      <c r="K31" s="136"/>
-      <c r="L31" s="134"/>
-      <c r="M31" s="135"/>
-      <c r="N31" s="135"/>
-      <c r="O31" s="136"/>
-      <c r="P31" s="142"/>
-      <c r="Q31" s="135"/>
-      <c r="R31" s="135"/>
-      <c r="S31" s="136"/>
-      <c r="T31" s="134"/>
-      <c r="U31" s="135"/>
-      <c r="V31" s="135"/>
-      <c r="W31" s="136"/>
-      <c r="X31" s="134"/>
-      <c r="Y31" s="135"/>
-      <c r="Z31" s="135"/>
-      <c r="AA31" s="136"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="B32" s="107"/>
-      <c r="C32" s="102" t="s">
-        <v>352</v>
-      </c>
-      <c r="D32" s="106"/>
-      <c r="E32" s="104"/>
-      <c r="F32" s="104"/>
-      <c r="G32" s="105"/>
-      <c r="H32" s="106"/>
-      <c r="I32" s="104"/>
-      <c r="J32" s="104"/>
-      <c r="K32" s="105"/>
-      <c r="L32" s="106"/>
-      <c r="M32" s="104"/>
-      <c r="N32" s="104"/>
-      <c r="O32" s="105"/>
-      <c r="P32" s="106"/>
-      <c r="Q32" s="143"/>
-      <c r="R32" s="104"/>
-      <c r="S32" s="105"/>
-      <c r="T32" s="106"/>
-      <c r="U32" s="104"/>
-      <c r="V32" s="104"/>
-      <c r="W32" s="105"/>
-      <c r="X32" s="106"/>
-      <c r="Y32" s="104"/>
-      <c r="Z32" s="104"/>
-      <c r="AA32" s="105"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="B33" s="125"/>
-      <c r="C33" s="126" t="s">
-        <v>353</v>
-      </c>
-      <c r="D33" s="127"/>
-      <c r="E33" s="128"/>
-      <c r="F33" s="128"/>
-      <c r="G33" s="129"/>
-      <c r="H33" s="127"/>
-      <c r="I33" s="128"/>
-      <c r="J33" s="128"/>
-      <c r="K33" s="129"/>
-      <c r="L33" s="127"/>
-      <c r="M33" s="128"/>
-      <c r="N33" s="128"/>
-      <c r="O33" s="129"/>
-      <c r="P33" s="127"/>
-      <c r="Q33" s="144"/>
-      <c r="R33" s="145"/>
-      <c r="S33" s="146"/>
-      <c r="T33" s="127"/>
-      <c r="U33" s="128"/>
-      <c r="V33" s="128"/>
-      <c r="W33" s="129"/>
-      <c r="X33" s="127"/>
-      <c r="Y33" s="128"/>
-      <c r="Z33" s="128"/>
-      <c r="AA33" s="129"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="B34" s="132" t="s">
-        <v>354</v>
-      </c>
-      <c r="C34" s="133" t="s">
-        <v>355</v>
-      </c>
-      <c r="D34" s="134"/>
-      <c r="E34" s="135"/>
-      <c r="F34" s="135"/>
-      <c r="G34" s="136"/>
-      <c r="H34" s="134"/>
-      <c r="I34" s="135"/>
-      <c r="J34" s="135"/>
-      <c r="K34" s="136"/>
-      <c r="L34" s="134"/>
-      <c r="M34" s="135"/>
-      <c r="N34" s="135"/>
-      <c r="O34" s="136"/>
-      <c r="P34" s="134"/>
-      <c r="Q34" s="135"/>
-      <c r="R34" s="135"/>
-      <c r="S34" s="147"/>
-      <c r="T34" s="148"/>
-      <c r="U34" s="135"/>
-      <c r="V34" s="135"/>
-      <c r="W34" s="136"/>
-      <c r="X34" s="134"/>
-      <c r="Y34" s="135"/>
-      <c r="Z34" s="135"/>
-      <c r="AA34" s="136"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="B35" s="107"/>
-      <c r="C35" s="102" t="s">
-        <v>356</v>
-      </c>
-      <c r="D35" s="106"/>
-      <c r="E35" s="104"/>
-      <c r="F35" s="104"/>
-      <c r="G35" s="105"/>
-      <c r="H35" s="106"/>
-      <c r="I35" s="104"/>
-      <c r="J35" s="104"/>
-      <c r="K35" s="105"/>
-      <c r="L35" s="106"/>
-      <c r="M35" s="104"/>
-      <c r="N35" s="104"/>
-      <c r="O35" s="105"/>
-      <c r="P35" s="106"/>
-      <c r="Q35" s="104"/>
-      <c r="R35" s="104"/>
-      <c r="S35" s="105"/>
-      <c r="T35" s="149"/>
-      <c r="U35" s="150"/>
-      <c r="V35" s="104"/>
-      <c r="W35" s="105"/>
-      <c r="X35" s="106"/>
-      <c r="Y35" s="104"/>
-      <c r="Z35" s="104"/>
-      <c r="AA35" s="105"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="B36" s="125"/>
-      <c r="C36" s="126" t="s">
-        <v>357</v>
-      </c>
-      <c r="D36" s="127"/>
-      <c r="E36" s="128"/>
-      <c r="F36" s="128"/>
-      <c r="G36" s="129"/>
-      <c r="H36" s="127"/>
-      <c r="I36" s="128"/>
-      <c r="J36" s="128"/>
-      <c r="K36" s="129"/>
-      <c r="L36" s="127"/>
-      <c r="M36" s="128"/>
-      <c r="N36" s="128"/>
-      <c r="O36" s="129"/>
-      <c r="P36" s="127"/>
-      <c r="Q36" s="128"/>
-      <c r="R36" s="128"/>
-      <c r="S36" s="129"/>
-      <c r="T36" s="127"/>
-      <c r="U36" s="128"/>
-      <c r="V36" s="151"/>
-      <c r="W36" s="152"/>
-      <c r="X36" s="127"/>
-      <c r="Y36" s="128"/>
-      <c r="Z36" s="128"/>
-      <c r="AA36" s="129"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="B37" s="132" t="s">
-        <v>358</v>
-      </c>
-      <c r="C37" s="133" t="s">
-        <v>359</v>
-      </c>
-      <c r="D37" s="134"/>
-      <c r="E37" s="135"/>
-      <c r="F37" s="135"/>
-      <c r="G37" s="136"/>
-      <c r="H37" s="134"/>
-      <c r="I37" s="135"/>
-      <c r="J37" s="135"/>
-      <c r="K37" s="136"/>
-      <c r="L37" s="134"/>
-      <c r="M37" s="135"/>
-      <c r="N37" s="135"/>
-      <c r="O37" s="136"/>
-      <c r="P37" s="134"/>
-      <c r="Q37" s="135"/>
-      <c r="R37" s="135"/>
-      <c r="S37" s="136"/>
-      <c r="T37" s="134"/>
-      <c r="U37" s="135"/>
-      <c r="V37" s="135"/>
-      <c r="W37" s="136"/>
-      <c r="X37" s="153"/>
-      <c r="Y37" s="135"/>
-      <c r="Z37" s="135"/>
-      <c r="AA37" s="136"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="B38" s="107"/>
-      <c r="C38" s="102" t="s">
-        <v>360</v>
-      </c>
-      <c r="D38" s="106"/>
-      <c r="E38" s="104"/>
-      <c r="F38" s="104"/>
-      <c r="G38" s="105"/>
-      <c r="H38" s="106"/>
-      <c r="I38" s="104"/>
-      <c r="J38" s="104"/>
-      <c r="K38" s="105"/>
-      <c r="L38" s="106"/>
-      <c r="M38" s="104"/>
-      <c r="N38" s="104"/>
-      <c r="O38" s="105"/>
-      <c r="P38" s="106"/>
-      <c r="Q38" s="104"/>
-      <c r="R38" s="104"/>
-      <c r="S38" s="105"/>
-      <c r="T38" s="106"/>
-      <c r="U38" s="104"/>
-      <c r="V38" s="104"/>
-      <c r="W38" s="105"/>
-      <c r="X38" s="106"/>
-      <c r="Y38" s="154"/>
-      <c r="Z38" s="104"/>
-      <c r="AA38" s="105"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="B39" s="155"/>
-      <c r="C39" s="156" t="s">
-        <v>361</v>
-      </c>
-      <c r="D39" s="157"/>
-      <c r="E39" s="158"/>
-      <c r="F39" s="158"/>
-      <c r="G39" s="159"/>
-      <c r="H39" s="157"/>
-      <c r="I39" s="158"/>
-      <c r="J39" s="158"/>
-      <c r="K39" s="159"/>
-      <c r="L39" s="157"/>
-      <c r="M39" s="158"/>
-      <c r="N39" s="158"/>
-      <c r="O39" s="159"/>
-      <c r="P39" s="157"/>
-      <c r="Q39" s="158"/>
-      <c r="R39" s="158"/>
-      <c r="S39" s="159"/>
-      <c r="T39" s="157"/>
-      <c r="U39" s="158"/>
-      <c r="V39" s="158"/>
-      <c r="W39" s="159"/>
-      <c r="X39" s="157"/>
-      <c r="Y39" s="158"/>
-      <c r="Z39" s="160"/>
-      <c r="AA39" s="161"/>
-    </row>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
-      <c r="R42" s="1"/>
-      <c r="S42" s="1"/>
-      <c r="T42" s="1"/>
-      <c r="U42" s="1"/>
-      <c r="V42" s="1"/>
-      <c r="W42" s="1"/>
-      <c r="X42" s="1"/>
-      <c r="Y42" s="1"/>
-      <c r="Z42" s="1"/>
-      <c r="AA42" s="1"/>
-      <c r="AB42" s="1"/>
-    </row>
+    <row r="42" ht="15.75" customHeight="1"/>
     <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="B44" s="162" t="s">
-        <v>362</v>
-      </c>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
-      <c r="I44" s="8"/>
-      <c r="J44" s="8"/>
-      <c r="K44" s="8"/>
-      <c r="L44" s="8"/>
-      <c r="M44" s="9"/>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="B45" s="163"/>
-      <c r="M45" s="164"/>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="B46" s="163"/>
-      <c r="M46" s="164"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="B47" s="163"/>
-      <c r="M47" s="164"/>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="B48" s="163"/>
-      <c r="M48" s="164"/>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="B49" s="163"/>
-      <c r="M49" s="164"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="B50" s="163"/>
-      <c r="M50" s="164"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="B51" s="163"/>
-      <c r="M51" s="164"/>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="B52" s="163"/>
-      <c r="M52" s="164"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="B53" s="163"/>
-      <c r="M53" s="164"/>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="B54" s="163"/>
-      <c r="M54" s="164"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="B55" s="163"/>
-      <c r="M55" s="164"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="B56" s="163"/>
-      <c r="M56" s="164"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="B57" s="163"/>
-      <c r="M57" s="164"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="B58" s="163"/>
-      <c r="M58" s="164"/>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="B59" s="163"/>
-      <c r="M59" s="164"/>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="B60" s="163"/>
-      <c r="M60" s="164"/>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="B61" s="163"/>
-      <c r="M61" s="164"/>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="B62" s="163"/>
-      <c r="M62" s="164"/>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="B63" s="163"/>
-      <c r="M63" s="164"/>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="B64" s="163"/>
-      <c r="M64" s="164"/>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="B65" s="163"/>
-      <c r="M65" s="164"/>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="B66" s="163"/>
-      <c r="M66" s="164"/>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="B67" s="163"/>
-      <c r="M67" s="164"/>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="B68" s="163"/>
-      <c r="M68" s="164"/>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="B69" s="163"/>
-      <c r="M69" s="164"/>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="B70" s="163"/>
-      <c r="M70" s="164"/>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="B71" s="163"/>
-      <c r="M71" s="164"/>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="B72" s="163"/>
-      <c r="M72" s="164"/>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="B73" s="163"/>
-      <c r="M73" s="164"/>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="B74" s="163"/>
-      <c r="M74" s="164"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="B75" s="163"/>
-      <c r="M75" s="164"/>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="B76" s="163"/>
-      <c r="M76" s="164"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="B77" s="163"/>
-      <c r="M77" s="164"/>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
-      <c r="B78" s="163"/>
-      <c r="M78" s="164"/>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="B79" s="163"/>
-      <c r="M79" s="164"/>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
-      <c r="B80" s="163"/>
-      <c r="M80" s="164"/>
-    </row>
-    <row r="81" ht="15.75" customHeight="1">
-      <c r="B81" s="163"/>
-      <c r="M81" s="164"/>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="B82" s="163"/>
-      <c r="M82" s="164"/>
-    </row>
-    <row r="83" ht="15.75" customHeight="1">
-      <c r="B83" s="12"/>
-      <c r="C83" s="13"/>
-      <c r="D83" s="13"/>
-      <c r="E83" s="13"/>
-      <c r="F83" s="13"/>
-      <c r="G83" s="13"/>
-      <c r="H83" s="13"/>
-      <c r="I83" s="13"/>
-      <c r="J83" s="13"/>
-      <c r="K83" s="13"/>
-      <c r="L83" s="13"/>
-      <c r="M83" s="14"/>
-    </row>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
     <row r="84" ht="15.75" customHeight="1"/>
     <row r="85" ht="15.75" customHeight="1"/>
     <row r="86" ht="15.75" customHeight="1"/>
@@ -9250,112 +7488,8 @@
     <row r="936" ht="15.75" customHeight="1"/>
     <row r="937" ht="15.75" customHeight="1"/>
     <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="B19:C20"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="H19:K19"/>
-    <mergeCell ref="L19:O19"/>
-    <mergeCell ref="P19:S19"/>
-    <mergeCell ref="T19:W19"/>
-    <mergeCell ref="X19:AA19"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="L20:L21"/>
-    <mergeCell ref="M20:M21"/>
-    <mergeCell ref="N20:N21"/>
-    <mergeCell ref="O20:O21"/>
-    <mergeCell ref="P20:P21"/>
-    <mergeCell ref="Q20:Q21"/>
-    <mergeCell ref="Y20:Y21"/>
-    <mergeCell ref="Z20:Z21"/>
-    <mergeCell ref="AA20:AA21"/>
-    <mergeCell ref="R20:R21"/>
-    <mergeCell ref="S20:S21"/>
-    <mergeCell ref="T20:T21"/>
-    <mergeCell ref="U20:U21"/>
-    <mergeCell ref="V20:V21"/>
-    <mergeCell ref="W20:W21"/>
-    <mergeCell ref="X20:X21"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B44:M83"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="J20:J21"/>
-  </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>